--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -581,7 +581,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,12 +591,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,17 +641,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="215">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,102 +52,123 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Пазарджик</t>
-  </si>
-  <si>
-    <t>Тракия</t>
-  </si>
-  <si>
-    <t>Сливен</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>Ямбол</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>София Резбарска</t>
-  </si>
-  <si>
-    <t>Долни Богров</t>
-  </si>
-  <si>
-    <t>Ахелой</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Шумен 1</t>
-  </si>
-  <si>
-    <t>Търговище</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1196 Пазарджик Царица Йоанна</t>
+  </si>
+  <si>
+    <t>1915 O5 Сливен</t>
+  </si>
+  <si>
+    <t>1142 Пазарджик Север</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1173 Ямбол</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1112 София Резбарска</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1164 София Д. Богров</t>
+  </si>
+  <si>
+    <t>1916 О5 Ахелой</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1912 O5, Шумен 1</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1139 София Ломско шосе</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>В9702ТА</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>B3018XK</t>
   </si>
   <si>
+    <t>СВ5723НB</t>
+  </si>
+  <si>
     <t>В5649НТ</t>
   </si>
   <si>
     <t>В5941ТН</t>
   </si>
   <si>
-    <t>СВ5723НB</t>
+    <t>В5091ТС</t>
   </si>
   <si>
     <t>В5038НТ</t>
   </si>
   <si>
-    <t>В5091ТС</t>
-  </si>
-  <si>
     <t>В9046НР</t>
   </si>
   <si>
+    <t>В5982XK</t>
+  </si>
+  <si>
+    <t>B5938TH</t>
+  </si>
+  <si>
+    <t>В4288ХА</t>
+  </si>
+  <si>
     <t>В6359ТЕ</t>
   </si>
   <si>
-    <t>В4288ХА</t>
-  </si>
-  <si>
-    <t>B5938TH</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>В1052НН</t>
   </si>
   <si>
-    <t>В5982XK</t>
-  </si>
-  <si>
     <t>В7430ТМ</t>
   </si>
   <si>
@@ -157,51 +181,57 @@
     <t>В8028НН</t>
   </si>
   <si>
+    <t>В0509ХА</t>
+  </si>
+  <si>
+    <t>В2573ХЕ</t>
+  </si>
+  <si>
+    <t>78970155027720170</t>
+  </si>
+  <si>
     <t>78970155027720113</t>
   </si>
   <si>
-    <t>78970155027720170</t>
-  </si>
-  <si>
     <t>78970153027721439</t>
   </si>
   <si>
+    <t>78970152027720144</t>
+  </si>
+  <si>
     <t>78970155027720097</t>
   </si>
   <si>
     <t>78970155027720030</t>
   </si>
   <si>
-    <t>78970152027720144</t>
+    <t>78970155027720105</t>
   </si>
   <si>
     <t>78970155027720022</t>
   </si>
   <si>
-    <t>78970155027720105</t>
-  </si>
-  <si>
     <t>78970155027720048</t>
   </si>
   <si>
+    <t>78970156027720822</t>
+  </si>
+  <si>
+    <t>78970155027720014</t>
+  </si>
+  <si>
+    <t>78970155027720162</t>
+  </si>
+  <si>
     <t>78970155027720139</t>
   </si>
   <si>
-    <t>78970155027720162</t>
-  </si>
-  <si>
-    <t>78970155027720014</t>
-  </si>
-  <si>
     <t>78970155027720188</t>
   </si>
   <si>
     <t>78970155027720121</t>
   </si>
   <si>
-    <t>78970156027720822</t>
-  </si>
-  <si>
     <t>78970155027720147</t>
   </si>
   <si>
@@ -214,136 +244,403 @@
     <t>78970155027720154</t>
   </si>
   <si>
+    <t>78970155027720063</t>
+  </si>
+  <si>
+    <t>78970151027720583</t>
+  </si>
+  <si>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-16 06:34:45</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:48:34</t>
-  </si>
-  <si>
-    <t>2026-06-16 15:18:59</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:52:18</t>
-  </si>
-  <si>
-    <t>2026-06-17 14:15:29</t>
-  </si>
-  <si>
-    <t>2026-06-17 15:48:59</t>
-  </si>
-  <si>
-    <t>2026-06-17 16:04:13</t>
-  </si>
-  <si>
-    <t>2026-06-18 11:04:47</t>
-  </si>
-  <si>
-    <t>2026-06-18 13:18:40</t>
-  </si>
-  <si>
-    <t>2026-06-18 14:06:35</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:28:32</t>
-  </si>
-  <si>
-    <t>2026-06-20 10:11:18</t>
-  </si>
-  <si>
-    <t>2026-06-22 07:35:15</t>
-  </si>
-  <si>
-    <t>2026-06-22 07:45:37</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:49:18</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:16:02</t>
-  </si>
-  <si>
-    <t>2026-06-22 15:12:43</t>
-  </si>
-  <si>
-    <t>2026-06-22 18:03:14</t>
-  </si>
-  <si>
-    <t>2026-06-23 05:17:05</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:24:52</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:27:35</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:12:26</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:57:46</t>
-  </si>
-  <si>
-    <t>2026-06-23 14:47:44</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:34:49</t>
-  </si>
-  <si>
-    <t>2026-06-24 06:57:28</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:54:43</t>
-  </si>
-  <si>
-    <t>2026-06-24 09:45:55</t>
-  </si>
-  <si>
-    <t>2026-06-24 09:56:52</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:43:03</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:04:10</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:51:44</t>
-  </si>
-  <si>
-    <t>2026-06-24 16:11:41</t>
-  </si>
-  <si>
-    <t>2026-06-25 04:53:26</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:09:28</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:40:07</t>
-  </si>
-  <si>
-    <t>2026-06-25 10:17:03</t>
-  </si>
-  <si>
-    <t>2026-06-25 13:14:45</t>
-  </si>
-  <si>
-    <t>2026-06-25 14:34:15</t>
-  </si>
-  <si>
-    <t>2026-06-25 14:36:59</t>
-  </si>
-  <si>
-    <t>2026-06-25 18:24:42</t>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>06:34:00</t>
+  </si>
+  <si>
+    <t>15:19:00</t>
+  </si>
+  <si>
+    <t>16:04:00</t>
+  </si>
+  <si>
+    <t>15:48:00</t>
+  </si>
+  <si>
+    <t>12:52:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>14:07:00</t>
+  </si>
+  <si>
+    <t>11:04:00</t>
+  </si>
+  <si>
+    <t>13:18:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>18:03:00</t>
+  </si>
+  <si>
+    <t>10:49:00</t>
+  </si>
+  <si>
+    <t>07:45:00</t>
+  </si>
+  <si>
+    <t>07:35:00</t>
+  </si>
+  <si>
+    <t>13:16:00</t>
+  </si>
+  <si>
+    <t>15:13:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>10:12:00</t>
+  </si>
+  <si>
+    <t>10:57:00</t>
+  </si>
+  <si>
+    <t>09:27:00</t>
+  </si>
+  <si>
+    <t>05:16:00</t>
+  </si>
+  <si>
+    <t>16:32:00</t>
+  </si>
+  <si>
+    <t>14:47:00</t>
+  </si>
+  <si>
+    <t>12:42:00</t>
+  </si>
+  <si>
+    <t>09:45:00</t>
+  </si>
+  <si>
+    <t>07:54:00</t>
+  </si>
+  <si>
+    <t>06:57:00</t>
+  </si>
+  <si>
+    <t>15:52:00</t>
+  </si>
+  <si>
+    <t>16:12:00</t>
+  </si>
+  <si>
+    <t>15:05:00</t>
+  </si>
+  <si>
+    <t>09:54:00</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>08:09:00</t>
+  </si>
+  <si>
+    <t>04:53:00</t>
+  </si>
+  <si>
+    <t>13:14:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
+  </si>
+  <si>
+    <t>14:33:00</t>
+  </si>
+  <si>
+    <t>18:24:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>09:37:00</t>
+  </si>
+  <si>
+    <t>13:43:00</t>
+  </si>
+  <si>
+    <t>09:53:00</t>
+  </si>
+  <si>
+    <t>12:59:00</t>
+  </si>
+  <si>
+    <t>04:48:00</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>11:16:00</t>
+  </si>
+  <si>
+    <t>11:37:00</t>
+  </si>
+  <si>
+    <t>16:36:00</t>
+  </si>
+  <si>
+    <t>16:51:00</t>
+  </si>
+  <si>
+    <t>16:06:00</t>
+  </si>
+  <si>
+    <t>16:22:00</t>
+  </si>
+  <si>
+    <t>10:04:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>15:59:00</t>
+  </si>
+  <si>
+    <t>13:25:00</t>
+  </si>
+  <si>
+    <t>16:38:00</t>
+  </si>
+  <si>
+    <t>14:12:00</t>
+  </si>
+  <si>
+    <t>13:22:00</t>
+  </si>
+  <si>
+    <t>3233442540 3233442540</t>
+  </si>
+  <si>
+    <t>3233432901 3233432901</t>
+  </si>
+  <si>
+    <t>3233446444 3233446444</t>
+  </si>
+  <si>
+    <t>3233476196 3233476196</t>
+  </si>
+  <si>
+    <t>3233481730 3233481730</t>
+  </si>
+  <si>
+    <t>3233486430 3233486430</t>
+  </si>
+  <si>
+    <t>3233479802 3233479802</t>
+  </si>
+  <si>
+    <t>3233535838 3233535838</t>
+  </si>
+  <si>
+    <t>3233532285 3233532285</t>
+  </si>
+  <si>
+    <t>3233537268 3233537268</t>
+  </si>
+  <si>
+    <t>3233521084 3233521084</t>
+  </si>
+  <si>
+    <t>3233641726 3233641726</t>
+  </si>
+  <si>
+    <t>3233654574 3233654574</t>
+  </si>
+  <si>
+    <t>3233710351 3233710351</t>
+  </si>
+  <si>
+    <t>3233709334 3233709334</t>
+  </si>
+  <si>
+    <t>3233715409 3233715409</t>
+  </si>
+  <si>
+    <t>3233724291 3233724291</t>
+  </si>
+  <si>
+    <t>3233733412 3233733412</t>
+  </si>
+  <si>
+    <t>3233761918 3233761918</t>
+  </si>
+  <si>
+    <t>3233762725 3233762725</t>
+  </si>
+  <si>
+    <t>3233693592 3233693592</t>
+  </si>
+  <si>
+    <t>3233705288 3233705288</t>
+  </si>
+  <si>
+    <t>3233759947 3233759947</t>
+  </si>
+  <si>
+    <t>3233769892 3233769892</t>
+  </si>
+  <si>
+    <t>3233774110 3233774110</t>
+  </si>
+  <si>
+    <t>3233786253 3233786253</t>
+  </si>
+  <si>
+    <t>3233795397 3233795397</t>
+  </si>
+  <si>
+    <t>3233800383 3233800383</t>
+  </si>
+  <si>
+    <t>3233810326 3233810326</t>
+  </si>
+  <si>
+    <t>3233823459 3233823459</t>
+  </si>
+  <si>
+    <t>3233824631 3233824631</t>
+  </si>
+  <si>
+    <t>3233817782 3233817782</t>
+  </si>
+  <si>
+    <t>3233821122 3233821122</t>
+  </si>
+  <si>
+    <t>3233842876 3233842876</t>
+  </si>
+  <si>
+    <t>3233826591 3233826591</t>
+  </si>
+  <si>
+    <t>3233864138 3233864138</t>
+  </si>
+  <si>
+    <t>3233860172 3233860172</t>
+  </si>
+  <si>
+    <t>3233863522 3233863522</t>
+  </si>
+  <si>
+    <t>3233860274 3233860274</t>
+  </si>
+  <si>
+    <t>3233830277 3233830277</t>
+  </si>
+  <si>
+    <t>3233870319 3233870319</t>
+  </si>
+  <si>
+    <t>3233932060 3233932060</t>
+  </si>
+  <si>
+    <t>3233940282 3233940282</t>
+  </si>
+  <si>
+    <t>3233883171 3233883171</t>
+  </si>
+  <si>
+    <t>3234054570 3234054570</t>
+  </si>
+  <si>
+    <t>3234060106 3234060106</t>
+  </si>
+  <si>
+    <t>3234050522 3234050522</t>
+  </si>
+  <si>
+    <t>3234063109 3234063109</t>
+  </si>
+  <si>
+    <t>3234087797 3234087797</t>
+  </si>
+  <si>
+    <t>3234097897 3234097897</t>
+  </si>
+  <si>
+    <t>3234099237 3234099237</t>
+  </si>
+  <si>
+    <t>3234109717 3234109717</t>
+  </si>
+  <si>
+    <t>3234110307 3234110307</t>
+  </si>
+  <si>
+    <t>3234100685 3234100685</t>
+  </si>
+  <si>
+    <t>3234107966 3234107966</t>
+  </si>
+  <si>
+    <t>3234081968 3234081968</t>
+  </si>
+  <si>
+    <t>3234082083 3234082083</t>
+  </si>
+  <si>
+    <t>3234078420 3234078420</t>
+  </si>
+  <si>
+    <t>3234098835 3234098835</t>
+  </si>
+  <si>
+    <t>3234097494 3234097494</t>
+  </si>
+  <si>
+    <t>3234114632 3234114632</t>
+  </si>
+  <si>
+    <t>3234112355 3234112355</t>
+  </si>
+  <si>
+    <t>3234113922 3234113922</t>
+  </si>
+  <si>
+    <t>3234077868 3234077868</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФУУДС ТРЕЙД ЕООД</t>
@@ -763,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -772,14 +1069,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -813,1338 +1113,1689 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>50.32</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.55</v>
+        <v>58.52</v>
+      </c>
+      <c r="G2" t="s">
+        <v>82</v>
       </c>
       <c r="H2">
-        <v>78</v>
+        <v>1.88</v>
       </c>
       <c r="I2" s="1">
-        <v>1.59</v>
+        <v>110.02</v>
       </c>
       <c r="J2">
-        <v>80.01000000000001</v>
-      </c>
-      <c r="K2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>1.88</v>
+      </c>
+      <c r="K2" s="1">
+        <v>110.02</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>58.52</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.88</v>
+        <v>50.32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
       </c>
       <c r="H3">
-        <v>110.02</v>
+        <v>1.55</v>
       </c>
       <c r="I3" s="1">
-        <v>1.88</v>
+        <v>78</v>
       </c>
       <c r="J3">
-        <v>110.02</v>
-      </c>
-      <c r="K3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1.59</v>
+      </c>
+      <c r="K3" s="1">
+        <v>80.01000000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3">
+        <v>216217</v>
+      </c>
+      <c r="N3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F4">
         <v>334.68</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4">
         <v>1.55</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>518.75</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.59</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>532.14</v>
       </c>
-      <c r="K4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46190</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F5">
-        <v>67.29000000000001</v>
-      </c>
-      <c r="G5" s="1">
+        <v>74.45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5">
         <v>1.54</v>
       </c>
-      <c r="H5">
-        <v>103.63</v>
-      </c>
       <c r="I5" s="1">
+        <v>114.65</v>
+      </c>
+      <c r="J5">
         <v>1.59</v>
       </c>
-      <c r="J5">
-        <v>106.99</v>
-      </c>
-      <c r="K5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" s="1">
+        <v>118.38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5">
+        <v>244240</v>
+      </c>
+      <c r="N5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46190</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>78.95</v>
-      </c>
-      <c r="G6" s="1">
+        <v>18.86</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6">
         <v>1.54</v>
       </c>
-      <c r="H6">
-        <v>121.58</v>
-      </c>
       <c r="I6" s="1">
+        <v>29.04</v>
+      </c>
+      <c r="J6">
         <v>1.59</v>
       </c>
-      <c r="J6">
-        <v>125.53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" s="1">
+        <v>29.99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M6">
+        <v>217007</v>
+      </c>
+      <c r="N6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46190</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F7">
-        <v>18.86</v>
-      </c>
-      <c r="G7" s="1">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7">
         <v>1.54</v>
       </c>
-      <c r="H7">
-        <v>29.04</v>
-      </c>
       <c r="I7" s="1">
+        <v>103.63</v>
+      </c>
+      <c r="J7">
         <v>1.59</v>
       </c>
-      <c r="J7">
-        <v>29.99</v>
-      </c>
-      <c r="K7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" s="1">
+        <v>106.99</v>
+      </c>
+      <c r="L7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7">
+        <v>241836</v>
+      </c>
+      <c r="N7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46190</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F8">
-        <v>74.45</v>
-      </c>
-      <c r="G8" s="1">
+        <v>78.95</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8">
         <v>1.54</v>
       </c>
-      <c r="H8">
-        <v>114.65</v>
-      </c>
       <c r="I8" s="1">
+        <v>121.58</v>
+      </c>
+      <c r="J8">
         <v>1.59</v>
       </c>
-      <c r="J8">
-        <v>118.38</v>
-      </c>
-      <c r="K8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="1">
+        <v>125.53</v>
+      </c>
+      <c r="L8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8">
+        <v>78858</v>
+      </c>
+      <c r="N8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46191</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F9">
-        <v>59.38</v>
-      </c>
-      <c r="G9" s="1">
+        <v>358.4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9">
         <v>1.54</v>
       </c>
-      <c r="H9">
-        <v>91.45</v>
-      </c>
       <c r="I9" s="1">
+        <v>551.9400000000001</v>
+      </c>
+      <c r="J9">
         <v>1.58</v>
       </c>
-      <c r="J9">
-        <v>93.81999999999999</v>
-      </c>
-      <c r="K9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="1">
+        <v>566.27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9">
+        <v>8997</v>
+      </c>
+      <c r="N9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46191</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F10">
-        <v>300</v>
-      </c>
-      <c r="G10" s="1">
+        <v>59.38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10">
         <v>1.54</v>
       </c>
-      <c r="H10">
-        <v>462</v>
-      </c>
       <c r="I10" s="1">
-        <v>1.57</v>
+        <v>91.45</v>
       </c>
       <c r="J10">
-        <v>471</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>1.58</v>
+      </c>
+      <c r="K10" s="1">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>91</v>
+      </c>
+      <c r="M10">
+        <v>318418</v>
+      </c>
+      <c r="N10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46191</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F11">
-        <v>358.4</v>
-      </c>
-      <c r="G11" s="1">
+        <v>300</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11">
         <v>1.54</v>
       </c>
-      <c r="H11">
-        <v>551.9400000000001</v>
-      </c>
       <c r="I11" s="1">
-        <v>1.58</v>
+        <v>462</v>
       </c>
       <c r="J11">
-        <v>566.27</v>
-      </c>
-      <c r="K11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>1.57</v>
+      </c>
+      <c r="K11" s="1">
+        <v>471</v>
+      </c>
+      <c r="L11" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11">
+        <v>833593</v>
+      </c>
+      <c r="N11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46192</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F12">
         <v>59.38</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12">
         <v>1.54</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>91.45</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.56</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>92.63</v>
       </c>
-      <c r="K12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12">
+        <v>677082</v>
+      </c>
+      <c r="N12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46193</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F13">
         <v>265.08</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13">
         <v>1.5</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>397.62</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.54</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>408.22</v>
       </c>
-      <c r="K13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>94</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46195</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F14">
-        <v>41.47</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1.47</v>
+        <v>59.6</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
       </c>
       <c r="H14">
-        <v>60.96</v>
+        <v>1.42</v>
       </c>
       <c r="I14" s="1">
-        <v>1.52</v>
+        <v>84.63</v>
       </c>
       <c r="J14">
-        <v>63.03</v>
-      </c>
-      <c r="K14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K14" s="1">
+        <v>90</v>
+      </c>
+      <c r="L14" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46195</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F15">
-        <v>32.11</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.42</v>
+        <v>72.89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>82</v>
       </c>
       <c r="H15">
-        <v>45.6</v>
+        <v>1.47</v>
       </c>
       <c r="I15" s="1">
-        <v>1.51</v>
+        <v>107.15</v>
       </c>
       <c r="J15">
-        <v>48.49</v>
-      </c>
-      <c r="K15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K15" s="1">
+        <v>110.79</v>
+      </c>
+      <c r="L15" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15">
+        <v>61420</v>
+      </c>
+      <c r="N15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46195</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F16">
-        <v>72.89</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.47</v>
+        <v>32.11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>82</v>
       </c>
       <c r="H16">
-        <v>107.15</v>
+        <v>1.42</v>
       </c>
       <c r="I16" s="1">
-        <v>1.52</v>
+        <v>45.6</v>
       </c>
       <c r="J16">
-        <v>110.79</v>
-      </c>
-      <c r="K16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K16" s="1">
+        <v>48.49</v>
+      </c>
+      <c r="L16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M16">
+        <v>130215</v>
+      </c>
+      <c r="N16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46195</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F17">
-        <v>57.49</v>
-      </c>
-      <c r="G17" s="1">
+        <v>41.47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17">
         <v>1.47</v>
       </c>
-      <c r="H17">
-        <v>84.51000000000001</v>
-      </c>
       <c r="I17" s="1">
+        <v>60.96</v>
+      </c>
+      <c r="J17">
         <v>1.52</v>
       </c>
-      <c r="J17">
-        <v>87.38</v>
-      </c>
-      <c r="K17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" s="1">
+        <v>63.03</v>
+      </c>
+      <c r="L17" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17">
+        <v>95362</v>
+      </c>
+      <c r="N17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46195</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F18">
-        <v>58.75</v>
-      </c>
-      <c r="G18" s="1">
+        <v>57.49</v>
+      </c>
+      <c r="G18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18">
         <v>1.47</v>
       </c>
-      <c r="H18">
-        <v>86.36</v>
-      </c>
       <c r="I18" s="1">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="J18">
         <v>1.52</v>
       </c>
-      <c r="J18">
-        <v>89.3</v>
-      </c>
-      <c r="K18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="K18" s="1">
+        <v>87.38</v>
+      </c>
+      <c r="L18" t="s">
+        <v>99</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46195</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F19">
-        <v>59.6</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1.42</v>
+        <v>58.75</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
       </c>
       <c r="H19">
-        <v>84.63</v>
+        <v>1.47</v>
       </c>
       <c r="I19" s="1">
-        <v>1.51</v>
+        <v>86.36</v>
       </c>
       <c r="J19">
-        <v>90</v>
-      </c>
-      <c r="K19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K19" s="1">
+        <v>89.3</v>
+      </c>
+      <c r="L19" t="s">
+        <v>100</v>
+      </c>
+      <c r="M19">
+        <v>230213</v>
+      </c>
+      <c r="N19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46196</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F20">
-        <v>67.62</v>
-      </c>
-      <c r="G20" s="1">
+        <v>80.36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20">
         <v>1.47</v>
       </c>
-      <c r="H20">
-        <v>99.40000000000001</v>
-      </c>
       <c r="I20" s="1">
+        <v>118.13</v>
+      </c>
+      <c r="J20">
         <v>1.52</v>
       </c>
-      <c r="J20">
-        <v>102.78</v>
-      </c>
-      <c r="K20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" s="1">
+        <v>122.15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>101</v>
+      </c>
+      <c r="M20">
+        <v>217140</v>
+      </c>
+      <c r="N20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46196</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F21">
-        <v>80.36</v>
-      </c>
-      <c r="G21" s="1">
+        <v>56.48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21">
         <v>1.47</v>
       </c>
-      <c r="H21">
-        <v>118.13</v>
-      </c>
       <c r="I21" s="1">
+        <v>83.03</v>
+      </c>
+      <c r="J21">
         <v>1.52</v>
       </c>
-      <c r="J21">
-        <v>122.15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" s="1">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="L21" t="s">
+        <v>102</v>
+      </c>
+      <c r="M21">
+        <v>244683</v>
+      </c>
+      <c r="N21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46196</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F22">
-        <v>77.98999999999999</v>
-      </c>
-      <c r="G22" s="1">
+        <v>68.87</v>
+      </c>
+      <c r="G22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22">
         <v>1.47</v>
       </c>
-      <c r="H22">
-        <v>114.65</v>
-      </c>
       <c r="I22" s="1">
+        <v>101.24</v>
+      </c>
+      <c r="J22">
         <v>1.52</v>
       </c>
-      <c r="J22">
-        <v>118.54</v>
-      </c>
-      <c r="K22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="K22" s="1">
+        <v>104.68</v>
+      </c>
+      <c r="L22" t="s">
+        <v>103</v>
+      </c>
+      <c r="M22">
+        <v>677517</v>
+      </c>
+      <c r="N22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46196</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F23">
-        <v>56.48</v>
-      </c>
-      <c r="G23" s="1">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23">
         <v>1.47</v>
       </c>
-      <c r="H23">
-        <v>83.03</v>
-      </c>
       <c r="I23" s="1">
+        <v>114.65</v>
+      </c>
+      <c r="J23">
         <v>1.52</v>
       </c>
-      <c r="J23">
-        <v>85.84999999999999</v>
-      </c>
-      <c r="K23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="K23" s="1">
+        <v>118.54</v>
+      </c>
+      <c r="L23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23">
+        <v>188768</v>
+      </c>
+      <c r="N23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46196</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F24">
-        <v>68.87</v>
-      </c>
-      <c r="G24" s="1">
+        <v>67.62</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24">
         <v>1.47</v>
       </c>
-      <c r="H24">
-        <v>101.24</v>
-      </c>
       <c r="I24" s="1">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="J24">
         <v>1.52</v>
       </c>
-      <c r="J24">
-        <v>104.68</v>
-      </c>
-      <c r="K24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="K24" s="1">
+        <v>102.78</v>
+      </c>
+      <c r="L24" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24">
+        <v>319020</v>
+      </c>
+      <c r="N24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46196</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F25">
-        <v>325.15</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1.47</v>
+        <v>85.15000000000001</v>
+      </c>
+      <c r="G25" t="s">
+        <v>82</v>
       </c>
       <c r="H25">
-        <v>477.97</v>
+        <v>1.78</v>
       </c>
       <c r="I25" s="1">
-        <v>1.52</v>
+        <v>151.57</v>
       </c>
       <c r="J25">
-        <v>494.23</v>
-      </c>
-      <c r="K25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>1.78</v>
+      </c>
+      <c r="K25" s="1">
+        <v>151.57</v>
+      </c>
+      <c r="L25" t="s">
+        <v>106</v>
+      </c>
+      <c r="M25">
+        <v>205792</v>
+      </c>
+      <c r="N25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46196</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F26">
-        <v>85.15000000000001</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1.78</v>
+        <v>325.15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>82</v>
       </c>
       <c r="H26">
-        <v>151.57</v>
+        <v>1.47</v>
       </c>
       <c r="I26" s="1">
-        <v>1.78</v>
+        <v>477.97</v>
       </c>
       <c r="J26">
-        <v>151.57</v>
-      </c>
-      <c r="K26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K26" s="1">
+        <v>494.23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>107</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46197</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F27">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="G27" s="1">
+        <v>72.78</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27">
         <v>1.46</v>
       </c>
-      <c r="H27">
-        <v>116.29</v>
-      </c>
       <c r="I27" s="1">
+        <v>106.26</v>
+      </c>
+      <c r="J27">
         <v>1.51</v>
       </c>
-      <c r="J27">
-        <v>120.27</v>
-      </c>
-      <c r="K27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="K27" s="1">
+        <v>109.9</v>
+      </c>
+      <c r="L27" t="s">
+        <v>108</v>
+      </c>
+      <c r="M27">
+        <v>245230</v>
+      </c>
+      <c r="N27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46197</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F28">
-        <v>40.11</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1.46</v>
+        <v>52.35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>82</v>
       </c>
       <c r="H28">
-        <v>58.56</v>
+        <v>1.77</v>
       </c>
       <c r="I28" s="1">
-        <v>1.51</v>
+        <v>92.66</v>
       </c>
       <c r="J28">
-        <v>60.57</v>
-      </c>
-      <c r="K28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>1.77</v>
+      </c>
+      <c r="K28" s="1">
+        <v>92.66</v>
+      </c>
+      <c r="L28" t="s">
+        <v>109</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46197</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F29">
-        <v>52.35</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1.77</v>
+        <v>40.11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
       </c>
       <c r="H29">
-        <v>92.66</v>
+        <v>1.46</v>
       </c>
       <c r="I29" s="1">
-        <v>1.77</v>
+        <v>58.56</v>
       </c>
       <c r="J29">
-        <v>92.66</v>
-      </c>
-      <c r="K29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K29" s="1">
+        <v>60.57</v>
+      </c>
+      <c r="L29" t="s">
+        <v>110</v>
+      </c>
+      <c r="M29">
+        <v>677764</v>
+      </c>
+      <c r="N29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46197</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F30">
-        <v>54.84</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.41</v>
+        <v>79.65000000000001</v>
+      </c>
+      <c r="G30" t="s">
+        <v>82</v>
       </c>
       <c r="H30">
-        <v>77.31999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="I30" s="1">
+        <v>116.29</v>
+      </c>
+      <c r="J30">
         <v>1.51</v>
       </c>
-      <c r="J30">
-        <v>82.81</v>
-      </c>
-      <c r="K30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="K30" s="1">
+        <v>120.27</v>
+      </c>
+      <c r="L30" t="s">
+        <v>111</v>
+      </c>
+      <c r="M30">
+        <v>217880</v>
+      </c>
+      <c r="N30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46197</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F31">
-        <v>72.78</v>
-      </c>
-      <c r="G31" s="1">
+        <v>75.91</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31">
         <v>1.46</v>
       </c>
-      <c r="H31">
-        <v>106.26</v>
-      </c>
       <c r="I31" s="1">
+        <v>110.83</v>
+      </c>
+      <c r="J31">
         <v>1.51</v>
       </c>
-      <c r="J31">
-        <v>109.9</v>
-      </c>
-      <c r="K31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="K31" s="1">
+        <v>114.62</v>
+      </c>
+      <c r="L31" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46197</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F32">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="G32" s="1">
+        <v>66.03</v>
+      </c>
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32">
         <v>1.46</v>
       </c>
-      <c r="H32">
-        <v>94.75</v>
-      </c>
       <c r="I32" s="1">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="J32">
         <v>1.51</v>
       </c>
-      <c r="J32">
-        <v>98</v>
-      </c>
-      <c r="K32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" s="1">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="L32" t="s">
+        <v>113</v>
+      </c>
+      <c r="M32">
+        <v>25739</v>
+      </c>
+      <c r="N32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46197</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F33">
-        <v>75.91</v>
-      </c>
-      <c r="G33" s="1">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33">
         <v>1.46</v>
       </c>
-      <c r="H33">
-        <v>110.83</v>
-      </c>
       <c r="I33" s="1">
+        <v>94.75</v>
+      </c>
+      <c r="J33">
         <v>1.51</v>
       </c>
-      <c r="J33">
-        <v>114.62</v>
-      </c>
-      <c r="K33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="K33" s="1">
+        <v>98</v>
+      </c>
+      <c r="L33" t="s">
+        <v>114</v>
+      </c>
+      <c r="M33">
+        <v>95930</v>
+      </c>
+      <c r="N33" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46197</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F34">
-        <v>66.03</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1.46</v>
+        <v>54.84</v>
+      </c>
+      <c r="G34" t="s">
+        <v>82</v>
       </c>
       <c r="H34">
-        <v>96.40000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="I34" s="1">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="J34">
         <v>1.51</v>
       </c>
-      <c r="J34">
-        <v>99.70999999999999</v>
-      </c>
-      <c r="K34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="K34" s="1">
+        <v>82.81</v>
+      </c>
+      <c r="L34" t="s">
+        <v>115</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46198</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F35">
-        <v>47.67</v>
-      </c>
-      <c r="G35" s="1">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="G35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35">
         <v>1.46</v>
       </c>
-      <c r="H35">
-        <v>69.59999999999999</v>
-      </c>
       <c r="I35" s="1">
-        <v>1.51</v>
+        <v>109.03</v>
       </c>
       <c r="J35">
-        <v>71.98</v>
-      </c>
-      <c r="K35" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>1.54</v>
+      </c>
+      <c r="K35" s="1">
+        <v>115.01</v>
+      </c>
+      <c r="L35" t="s">
+        <v>116</v>
+      </c>
+      <c r="M35">
+        <v>218606</v>
+      </c>
+      <c r="N35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46198</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F36">
         <v>18.94</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36">
         <v>1.46</v>
       </c>
-      <c r="H36">
+      <c r="I36" s="1">
         <v>27.65</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36">
         <v>1.51</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="1">
         <v>28.6</v>
       </c>
-      <c r="K36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" t="s">
+        <v>117</v>
+      </c>
+      <c r="M36">
+        <v>96155</v>
+      </c>
+      <c r="N36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46198</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F37">
-        <v>28.99</v>
-      </c>
-      <c r="G37" s="1">
+        <v>47.67</v>
+      </c>
+      <c r="G37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37">
         <v>1.46</v>
       </c>
-      <c r="H37">
-        <v>42.33</v>
-      </c>
       <c r="I37" s="1">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J37">
         <v>1.51</v>
       </c>
-      <c r="J37">
-        <v>43.77</v>
-      </c>
-      <c r="K37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="K37" s="1">
+        <v>71.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>118</v>
+      </c>
+      <c r="M37">
+        <v>319463</v>
+      </c>
+      <c r="N37" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46198</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F38">
-        <v>74.68000000000001</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1.46</v>
+        <v>27.34</v>
+      </c>
+      <c r="G38" t="s">
+        <v>82</v>
       </c>
       <c r="H38">
-        <v>109.03</v>
+        <v>1.41</v>
       </c>
       <c r="I38" s="1">
-        <v>1.54</v>
+        <v>38.55</v>
       </c>
       <c r="J38">
-        <v>115.01</v>
-      </c>
-      <c r="K38" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K38" s="1">
+        <v>41.28</v>
+      </c>
+      <c r="L38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46198</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F39">
-        <v>27.34</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1.41</v>
+        <v>57.51</v>
+      </c>
+      <c r="G39" t="s">
+        <v>82</v>
       </c>
       <c r="H39">
-        <v>38.55</v>
+        <v>1.46</v>
       </c>
       <c r="I39" s="1">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="J39">
         <v>1.51</v>
       </c>
-      <c r="J39">
-        <v>41.28</v>
-      </c>
-      <c r="K39" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="K39" s="1">
+        <v>86.84</v>
+      </c>
+      <c r="L39" t="s">
+        <v>120</v>
+      </c>
+      <c r="M39">
+        <v>242318</v>
+      </c>
+      <c r="N39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46198</v>
       </c>
@@ -2152,214 +2803,1317 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F40">
-        <v>25.46</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1.41</v>
+        <v>28.99</v>
+      </c>
+      <c r="G40" t="s">
+        <v>82</v>
       </c>
       <c r="H40">
-        <v>35.9</v>
+        <v>1.46</v>
       </c>
       <c r="I40" s="1">
+        <v>42.33</v>
+      </c>
+      <c r="J40">
         <v>1.51</v>
       </c>
-      <c r="J40">
-        <v>38.44</v>
-      </c>
-      <c r="K40" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="K40" s="1">
+        <v>43.77</v>
+      </c>
+      <c r="L40" t="s">
+        <v>121</v>
+      </c>
+      <c r="M40">
+        <v>420594</v>
+      </c>
+      <c r="N40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46198</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F41">
-        <v>57.51</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.46</v>
+        <v>25.46</v>
+      </c>
+      <c r="G41" t="s">
+        <v>82</v>
       </c>
       <c r="H41">
-        <v>83.95999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="I41" s="1">
+        <v>35.9</v>
+      </c>
+      <c r="J41">
         <v>1.51</v>
       </c>
-      <c r="J41">
-        <v>86.84</v>
-      </c>
-      <c r="K41" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="K41" s="1">
+        <v>38.44</v>
+      </c>
+      <c r="L41" t="s">
+        <v>122</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46198</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F42">
         <v>329.64</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" t="s">
+        <v>82</v>
+      </c>
+      <c r="H42">
         <v>1.46</v>
       </c>
-      <c r="H42">
+      <c r="I42" s="1">
         <v>481.27</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42">
         <v>1.51</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="1">
         <v>497.76</v>
       </c>
-      <c r="K42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="5" t="s">
+      <c r="L42" t="s">
+        <v>123</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43">
+        <v>73.02</v>
+      </c>
+      <c r="G43" t="s">
+        <v>82</v>
+      </c>
+      <c r="H43">
+        <v>1.44</v>
+      </c>
+      <c r="I43" s="1">
+        <v>105.15</v>
+      </c>
+      <c r="J43">
+        <v>1.51</v>
+      </c>
+      <c r="K43" s="1">
+        <v>110.26</v>
+      </c>
+      <c r="L43" t="s">
+        <v>87</v>
+      </c>
+      <c r="M43">
+        <v>206473</v>
+      </c>
+      <c r="N43" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44">
+        <v>60.85</v>
+      </c>
+      <c r="G44" t="s">
+        <v>82</v>
+      </c>
+      <c r="H44">
+        <v>1.44</v>
+      </c>
+      <c r="I44" s="1">
+        <v>87.62</v>
+      </c>
+      <c r="J44">
+        <v>1.51</v>
+      </c>
+      <c r="K44" s="1">
+        <v>91.88</v>
+      </c>
+      <c r="L44" t="s">
+        <v>124</v>
+      </c>
+      <c r="M44">
+        <v>245720</v>
+      </c>
+      <c r="N44" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" t="s">
+        <v>79</v>
+      </c>
+      <c r="F45">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="G45" t="s">
+        <v>82</v>
+      </c>
+      <c r="H45">
+        <v>1.44</v>
+      </c>
+      <c r="I45" s="1">
+        <v>96.13</v>
+      </c>
+      <c r="J45">
+        <v>1.51</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100.81</v>
+      </c>
+      <c r="L45" t="s">
+        <v>125</v>
+      </c>
+      <c r="M45">
+        <v>678228</v>
+      </c>
+      <c r="N45" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B46" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F46">
+        <v>83.42</v>
+      </c>
+      <c r="G46" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46">
+        <v>1.43</v>
+      </c>
+      <c r="I46" s="1">
+        <v>119.29</v>
+      </c>
+      <c r="J46">
+        <v>1.54</v>
+      </c>
+      <c r="K46" s="1">
+        <v>128.47</v>
+      </c>
+      <c r="L46" t="s">
+        <v>126</v>
+      </c>
+      <c r="M46">
+        <v>219460</v>
+      </c>
+      <c r="N46" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47">
+        <v>40.52</v>
+      </c>
+      <c r="G47" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47">
+        <v>1.43</v>
+      </c>
+      <c r="I47" s="1">
+        <v>57.94</v>
+      </c>
+      <c r="J47">
+        <v>1.51</v>
+      </c>
+      <c r="K47" s="1">
+        <v>61.19</v>
+      </c>
+      <c r="L47" t="s">
+        <v>127</v>
+      </c>
+      <c r="M47">
+        <v>245954</v>
+      </c>
+      <c r="N47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" t="s">
+        <v>79</v>
+      </c>
+      <c r="F48">
+        <v>57.9</v>
+      </c>
+      <c r="G48" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48">
+        <v>1.43</v>
+      </c>
+      <c r="I48" s="1">
+        <v>82.8</v>
+      </c>
+      <c r="J48">
+        <v>1.51</v>
+      </c>
+      <c r="K48" s="1">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="L48" t="s">
+        <v>128</v>
+      </c>
+      <c r="M48">
+        <v>96762</v>
+      </c>
+      <c r="N48" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49">
+        <v>51.47</v>
+      </c>
+      <c r="G49" t="s">
+        <v>82</v>
+      </c>
+      <c r="H49">
+        <v>1.43</v>
+      </c>
+      <c r="I49" s="1">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="J49">
+        <v>1.51</v>
+      </c>
+      <c r="K49" s="1">
+        <v>77.72</v>
+      </c>
+      <c r="L49" t="s">
+        <v>129</v>
+      </c>
+      <c r="M49">
+        <v>319890</v>
+      </c>
+      <c r="N49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50">
+        <v>270.8</v>
+      </c>
+      <c r="G50" t="s">
+        <v>82</v>
+      </c>
+      <c r="H50">
+        <v>1.43</v>
+      </c>
+      <c r="I50" s="1">
+        <v>387.24</v>
+      </c>
+      <c r="J50">
+        <v>1.54</v>
+      </c>
+      <c r="K50" s="1">
+        <v>417.03</v>
+      </c>
+      <c r="L50" t="s">
+        <v>130</v>
+      </c>
+      <c r="M50">
+        <v>837288</v>
+      </c>
+      <c r="N50" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51">
+        <v>53.33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51">
+        <v>1.39</v>
+      </c>
+      <c r="I51" s="1">
+        <v>74.13</v>
+      </c>
+      <c r="J51">
+        <v>1.5</v>
+      </c>
+      <c r="K51" s="1">
+        <v>80</v>
+      </c>
+      <c r="L51" t="s">
+        <v>131</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B52" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52">
+        <v>20.59</v>
+      </c>
+      <c r="G52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H52">
+        <v>1.43</v>
+      </c>
+      <c r="I52" s="1">
+        <v>29.44</v>
+      </c>
+      <c r="J52">
+        <v>1.51</v>
+      </c>
+      <c r="K52" s="1">
+        <v>31.09</v>
+      </c>
+      <c r="L52" t="s">
+        <v>132</v>
+      </c>
+      <c r="M52">
+        <v>206682</v>
+      </c>
+      <c r="N52" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" t="s">
+        <v>80</v>
+      </c>
+      <c r="F53">
+        <v>30.58</v>
+      </c>
+      <c r="G53" t="s">
+        <v>82</v>
+      </c>
+      <c r="H53">
+        <v>1.39</v>
+      </c>
+      <c r="I53" s="1">
+        <v>42.51</v>
+      </c>
+      <c r="J53">
+        <v>1.5</v>
+      </c>
+      <c r="K53" s="1">
+        <v>45.87</v>
+      </c>
+      <c r="L53" t="s">
+        <v>133</v>
+      </c>
+      <c r="M53">
+        <v>229030</v>
+      </c>
+      <c r="N53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54">
+        <v>28.61</v>
+      </c>
+      <c r="G54" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54">
+        <v>0.66</v>
+      </c>
+      <c r="I54" s="1">
+        <v>18.88</v>
+      </c>
+      <c r="J54">
+        <v>0.66</v>
+      </c>
+      <c r="K54" s="1">
+        <v>18.88</v>
+      </c>
+      <c r="L54" t="s">
+        <v>133</v>
+      </c>
+      <c r="M54">
+        <v>229030</v>
+      </c>
+      <c r="N54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" t="s">
+        <v>80</v>
+      </c>
+      <c r="F55">
+        <v>10.54</v>
+      </c>
+      <c r="G55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H55">
+        <v>1.39</v>
+      </c>
+      <c r="I55" s="1">
+        <v>14.65</v>
+      </c>
+      <c r="J55">
+        <v>1.5</v>
+      </c>
+      <c r="K55" s="1">
+        <v>15.81</v>
+      </c>
+      <c r="L55" t="s">
+        <v>134</v>
+      </c>
+      <c r="M55">
+        <v>257372</v>
+      </c>
+      <c r="N55" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56">
+        <v>49.22</v>
+      </c>
+      <c r="G56" t="s">
+        <v>82</v>
+      </c>
+      <c r="H56">
+        <v>1.43</v>
+      </c>
+      <c r="I56" s="1">
+        <v>70.38</v>
+      </c>
+      <c r="J56">
+        <v>1.51</v>
+      </c>
+      <c r="K56" s="1">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="L56" t="s">
+        <v>121</v>
+      </c>
+      <c r="M56">
+        <v>246328</v>
+      </c>
+      <c r="N56" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B57" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" t="s">
+        <v>60</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57">
+        <v>50.01</v>
+      </c>
+      <c r="G57" t="s">
+        <v>82</v>
+      </c>
+      <c r="H57">
+        <v>1.43</v>
+      </c>
+      <c r="I57" s="1">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="J57">
+        <v>1.51</v>
+      </c>
+      <c r="K57" s="1">
+        <v>75.52</v>
+      </c>
+      <c r="L57" t="s">
+        <v>135</v>
+      </c>
+      <c r="M57">
+        <v>2467825</v>
+      </c>
+      <c r="N57" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" t="s">
+        <v>80</v>
+      </c>
+      <c r="F58">
+        <v>21.76</v>
+      </c>
+      <c r="G58" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58">
+        <v>1.39</v>
+      </c>
+      <c r="I58" s="1">
+        <v>30.25</v>
+      </c>
+      <c r="J58">
+        <v>1.5</v>
+      </c>
+      <c r="K58" s="1">
+        <v>32.64</v>
+      </c>
+      <c r="L58" t="s">
+        <v>136</v>
+      </c>
+      <c r="M58">
+        <v>130629</v>
+      </c>
+      <c r="N58" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59">
+        <v>65.19</v>
+      </c>
+      <c r="G59" t="s">
+        <v>82</v>
+      </c>
+      <c r="H59">
+        <v>1.43</v>
+      </c>
+      <c r="I59" s="1">
+        <v>93.22</v>
+      </c>
+      <c r="J59">
+        <v>1.51</v>
+      </c>
+      <c r="K59" s="1">
+        <v>98.44</v>
+      </c>
+      <c r="L59" t="s">
+        <v>137</v>
+      </c>
+      <c r="M59">
+        <v>61871</v>
+      </c>
+      <c r="N59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60">
+        <v>58.41</v>
+      </c>
+      <c r="G60" t="s">
+        <v>82</v>
+      </c>
+      <c r="H60">
+        <v>1.43</v>
+      </c>
+      <c r="I60" s="1">
+        <v>83.53</v>
+      </c>
+      <c r="J60">
+        <v>1.51</v>
+      </c>
+      <c r="K60" s="1">
+        <v>88.2</v>
+      </c>
+      <c r="L60" t="s">
+        <v>138</v>
+      </c>
+      <c r="M60">
+        <v>420935</v>
+      </c>
+      <c r="N60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61">
+        <v>59.82</v>
+      </c>
+      <c r="G61" t="s">
+        <v>82</v>
+      </c>
+      <c r="H61">
+        <v>1.43</v>
+      </c>
+      <c r="I61" s="1">
+        <v>85.54000000000001</v>
+      </c>
+      <c r="J61">
+        <v>1.51</v>
+      </c>
+      <c r="K61" s="1">
+        <v>90.33</v>
+      </c>
+      <c r="L61" t="s">
+        <v>139</v>
+      </c>
+      <c r="M61">
+        <v>678664</v>
+      </c>
+      <c r="N61" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62">
+        <v>361.6</v>
+      </c>
+      <c r="G62" t="s">
+        <v>82</v>
+      </c>
+      <c r="H62">
+        <v>1.43</v>
+      </c>
+      <c r="I62" s="1">
+        <v>517.09</v>
+      </c>
+      <c r="J62">
+        <v>1.51</v>
+      </c>
+      <c r="K62" s="1">
+        <v>546.02</v>
+      </c>
+      <c r="L62" t="s">
+        <v>140</v>
+      </c>
+      <c r="M62">
+        <v>10088</v>
+      </c>
+      <c r="N62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B63" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" t="s">
+        <v>72</v>
+      </c>
+      <c r="E63" t="s">
+        <v>79</v>
+      </c>
+      <c r="F63">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="G63" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63">
+        <v>1.43</v>
+      </c>
+      <c r="I63" s="1">
+        <v>111.88</v>
+      </c>
+      <c r="J63">
+        <v>1.51</v>
+      </c>
+      <c r="K63" s="1">
+        <v>118.14</v>
+      </c>
+      <c r="L63" t="s">
+        <v>141</v>
+      </c>
+      <c r="M63">
+        <v>189206</v>
+      </c>
+      <c r="N63" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64">
+        <v>59.26</v>
+      </c>
+      <c r="G64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H64">
+        <v>1.43</v>
+      </c>
+      <c r="I64" s="1">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="J64">
+        <v>1.51</v>
+      </c>
+      <c r="K64" s="1">
+        <v>89.48</v>
+      </c>
+      <c r="L64" t="s">
+        <v>142</v>
+      </c>
+      <c r="M64">
+        <v>220070</v>
+      </c>
+      <c r="N64" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65">
+        <v>57.88</v>
+      </c>
+      <c r="G65" t="s">
+        <v>82</v>
+      </c>
+      <c r="H65">
+        <v>1.43</v>
+      </c>
+      <c r="I65" s="1">
+        <v>82.77</v>
+      </c>
+      <c r="J65">
+        <v>1.51</v>
+      </c>
+      <c r="K65" s="1">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="L65" t="s">
+        <v>143</v>
+      </c>
+      <c r="M65">
+        <v>230619</v>
+      </c>
+      <c r="N65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66">
+        <v>41.47</v>
+      </c>
+      <c r="G66" t="s">
+        <v>82</v>
+      </c>
+      <c r="H66">
+        <v>1.43</v>
+      </c>
+      <c r="I66" s="1">
+        <v>59.3</v>
+      </c>
+      <c r="J66">
+        <v>1.51</v>
+      </c>
+      <c r="K66" s="1">
+        <v>62.62</v>
+      </c>
+      <c r="L66" t="s">
+        <v>144</v>
+      </c>
+      <c r="M66">
+        <v>242587</v>
+      </c>
+      <c r="N66" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="7">
+        <v>5137.1</v>
+      </c>
+      <c r="C71" s="7">
+        <v>52</v>
+      </c>
+      <c r="D71" s="8">
+        <v>1.4774</v>
+      </c>
+      <c r="E71" s="7">
+        <v>7589.61</v>
+      </c>
+      <c r="F71" s="7">
+        <v>7887.09</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="7">
+        <v>315.56</v>
+      </c>
+      <c r="C72" s="7">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="7">
-        <v>3530.67</v>
-      </c>
-      <c r="C47" s="7">
-        <v>33</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1.4984</v>
-      </c>
-      <c r="E47" s="7">
-        <v>5290.44</v>
-      </c>
-      <c r="F47" s="7">
-        <v>5450.74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" s="7">
-        <v>199.35</v>
-      </c>
-      <c r="C48" s="7">
-        <v>5</v>
-      </c>
-      <c r="D48" s="8">
-        <v>1.4146</v>
-      </c>
-      <c r="E48" s="7">
-        <v>282</v>
-      </c>
-      <c r="F48" s="7">
-        <v>301.02</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="7">
+      <c r="D72" s="8">
+        <v>1.4056</v>
+      </c>
+      <c r="E72" s="7">
+        <v>443.54</v>
+      </c>
+      <c r="F72" s="7">
+        <v>475.34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="7">
         <v>196.02</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C73" s="7">
         <v>3</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D73" s="8">
         <v>1.8072</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E73" s="7">
         <v>354.25</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F73" s="7">
         <v>354.25</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="10">
-        <v>3926.04</v>
-      </c>
-      <c r="C50" s="10">
-        <v>41</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="10">
-        <v>5926.69</v>
-      </c>
-      <c r="F50" s="10">
-        <v>6106.01</v>
+    <row r="74" spans="1:14">
+      <c r="A74" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="7">
+        <v>28.61</v>
+      </c>
+      <c r="C74" s="7">
+        <v>1</v>
+      </c>
+      <c r="D74" s="8">
+        <v>0.6599</v>
+      </c>
+      <c r="E74" s="7">
+        <v>18.88</v>
+      </c>
+      <c r="F74" s="7">
+        <v>18.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" s="10">
+        <v>5677.29</v>
+      </c>
+      <c r="C75" s="10">
+        <v>65</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="10">
+        <v>8406.280000000001</v>
+      </c>
+      <c r="F75" s="10">
+        <v>8735.559999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
   <si>
     <t>Дата</t>
   </si>
@@ -55,298 +55,265 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Пазарджик</t>
-  </si>
-  <si>
-    <t>Тракия</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>София Резбарска</t>
-  </si>
-  <si>
-    <t>Долни Богров</t>
-  </si>
-  <si>
-    <t>Сливен</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Радиново</t>
-  </si>
-  <si>
-    <t>Бургас езеро</t>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1178 Русе, бул. България</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1196 Пазарджик Царица Йоанна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1173 Ямбол</t>
+  </si>
+  <si>
+    <t>1927 Пирдоп</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1139 София Ломско шосе</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1112 София Резбарска</t>
+  </si>
+  <si>
+    <t>В5941ТН</t>
+  </si>
+  <si>
+    <t>В9046НР</t>
+  </si>
+  <si>
+    <t>В5038НТ</t>
+  </si>
+  <si>
+    <t>В8028НН</t>
+  </si>
+  <si>
+    <t>В6359ТЕ</t>
   </si>
   <si>
     <t>В9702ТА</t>
   </si>
   <si>
-    <t>1</t>
+    <t>В4288ХА</t>
+  </si>
+  <si>
+    <t>В5091ТС</t>
+  </si>
+  <si>
+    <t>B5938TH</t>
+  </si>
+  <si>
+    <t>В7430ТМ</t>
+  </si>
+  <si>
+    <t>В1052НН</t>
+  </si>
+  <si>
+    <t>В6957НТ</t>
+  </si>
+  <si>
+    <t>В6364ТЕ</t>
   </si>
   <si>
     <t>В5649НТ</t>
   </si>
   <si>
-    <t>В5941ТН</t>
-  </si>
-  <si>
-    <t>В5038НТ</t>
-  </si>
-  <si>
-    <t>В5091ТС</t>
-  </si>
-  <si>
-    <t>В9046НР</t>
-  </si>
-  <si>
-    <t>В6359ТЕ</t>
-  </si>
-  <si>
-    <t>В4288ХА</t>
-  </si>
-  <si>
-    <t>B5938TH</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>В1052НН</t>
-  </si>
-  <si>
-    <t>В7430ТМ</t>
-  </si>
-  <si>
-    <t>В6957НТ</t>
-  </si>
-  <si>
-    <t>В6364ТЕ</t>
-  </si>
-  <si>
-    <t>В8028НН</t>
-  </si>
-  <si>
     <t>В0509ХА</t>
   </si>
   <si>
+    <t>78970155027720030</t>
+  </si>
+  <si>
+    <t>78970155027720048</t>
+  </si>
+  <si>
+    <t>78970155027720022</t>
+  </si>
+  <si>
+    <t>78970155027720154</t>
+  </si>
+  <si>
+    <t>78970155027720139</t>
+  </si>
+  <si>
     <t>78970155027720113</t>
   </si>
   <si>
-    <t>78970155027720170</t>
+    <t>78970155027720162</t>
+  </si>
+  <si>
+    <t>78970155027720105</t>
+  </si>
+  <si>
+    <t>78970155027720014</t>
+  </si>
+  <si>
+    <t>78970155027720147</t>
+  </si>
+  <si>
+    <t>78970155027720121</t>
+  </si>
+  <si>
+    <t>78970155027720089</t>
+  </si>
+  <si>
+    <t>78970155027720055</t>
   </si>
   <si>
     <t>78970155027720097</t>
   </si>
   <si>
-    <t>78970155027720030</t>
-  </si>
-  <si>
-    <t>78970155027720022</t>
-  </si>
-  <si>
-    <t>78970155027720105</t>
-  </si>
-  <si>
-    <t>78970155027720048</t>
-  </si>
-  <si>
-    <t>78970155027720139</t>
-  </si>
-  <si>
-    <t>78970155027720162</t>
-  </si>
-  <si>
-    <t>78970155027720014</t>
-  </si>
-  <si>
-    <t>78970155027720188</t>
-  </si>
-  <si>
-    <t>78970155027720121</t>
-  </si>
-  <si>
-    <t>78970155027720147</t>
-  </si>
-  <si>
-    <t>78970155027720089</t>
-  </si>
-  <si>
-    <t>78970155027720055</t>
-  </si>
-  <si>
-    <t>78970155027720154</t>
-  </si>
-  <si>
     <t>78970155027720063</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>10:28</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>05:17</t>
-  </si>
-  <si>
-    <t>09:24</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>06:57</t>
-  </si>
-  <si>
-    <t>07:54</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>15:04</t>
-  </si>
-  <si>
-    <t>15:52</t>
-  </si>
-  <si>
-    <t>16:12</t>
-  </si>
-  <si>
-    <t>04:53</t>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>04:38</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>04:43</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>10:43</t>
+  </si>
+  <si>
+    <t>13:51</t>
   </si>
   <si>
     <t>08:09</t>
   </si>
   <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>09:37</t>
-  </si>
-  <si>
-    <t>04:49</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:44</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>13:23</t>
-  </si>
-  <si>
-    <t>13:26</t>
-  </si>
-  <si>
-    <t>14:13</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>16:38</t>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>05:01</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>13:21</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
+    <t>15:37</t>
+  </si>
+  <si>
+    <t>16:33</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФУУДС ТРЕЙД ЕООД</t>
@@ -766,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -827,7 +794,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3">
-        <v>46189</v>
+        <v>46204</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -836,39 +803,39 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F2">
-        <v>50.32</v>
+        <v>68.37</v>
       </c>
       <c r="G2" s="1">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="H2">
-        <v>78</v>
+        <v>97.77</v>
       </c>
       <c r="I2" s="1">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J2">
-        <v>80.01000000000001</v>
+        <v>103.24</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L2">
-        <v>216217</v>
+        <v>79800</v>
       </c>
       <c r="M2">
-        <v>197630</v>
+        <v>207482</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46189</v>
+        <v>46204</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -877,39 +844,39 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F3">
-        <v>58.52</v>
+        <v>50.09</v>
       </c>
       <c r="G3" s="1">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="H3">
-        <v>110.02</v>
+        <v>71.63</v>
       </c>
       <c r="I3" s="1">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="J3">
-        <v>110.02</v>
+        <v>77.14</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>679000</v>
       </c>
       <c r="M3">
-        <v>248378</v>
+        <v>276852</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46190</v>
+        <v>46205</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -918,39 +885,39 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F4">
-        <v>67.29000000000001</v>
+        <v>75.97</v>
       </c>
       <c r="G4" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H4">
-        <v>103.63</v>
+        <v>108.64</v>
       </c>
       <c r="I4" s="1">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J4">
-        <v>106.99</v>
+        <v>114.71</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L4">
-        <v>241836</v>
+        <v>320497</v>
       </c>
       <c r="M4">
-        <v>220274</v>
+        <v>92835</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46190</v>
+        <v>46205</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -959,1930 +926,1623 @@
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>78.95</v>
+        <v>59.14</v>
       </c>
       <c r="G5" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H5">
-        <v>121.58</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J5">
-        <v>125.53</v>
+        <v>89.3</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L5">
-        <v>78858</v>
+        <v>421300</v>
       </c>
       <c r="M5">
-        <v>198190</v>
+        <v>280171</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="3">
-        <v>46190</v>
+        <v>46205</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F6">
-        <v>18.86</v>
+        <v>65.19</v>
       </c>
       <c r="G6" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H6">
-        <v>29.04</v>
+        <v>93.22</v>
       </c>
       <c r="I6" s="1">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>29.99</v>
+        <v>98.44</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L6">
-        <v>217007</v>
+        <v>679451</v>
       </c>
       <c r="M6">
-        <v>239834</v>
+        <v>121746</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3">
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F7">
-        <v>59.38</v>
+        <v>59.12</v>
       </c>
       <c r="G7" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H7">
-        <v>91.45</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="J7">
-        <v>93.81999999999999</v>
+        <v>89.27</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L7">
-        <v>318418</v>
+        <v>175703</v>
       </c>
       <c r="M7">
-        <v>88960</v>
+        <v>126738</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="3">
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F8">
-        <v>358.4</v>
+        <v>75.33</v>
       </c>
       <c r="G8" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H8">
-        <v>551.9400000000001</v>
+        <v>107.72</v>
       </c>
       <c r="I8" s="1">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="J8">
-        <v>566.27</v>
+        <v>113.75</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L8">
-        <v>8997</v>
+        <v>220850</v>
       </c>
       <c r="M8">
-        <v>267219</v>
+        <v>205003</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="3">
-        <v>46192</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9">
-        <v>59.38</v>
+        <v>52.96</v>
       </c>
       <c r="G9" s="1">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H9">
-        <v>91.45</v>
+        <v>75.73</v>
       </c>
       <c r="I9" s="1">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>92.63</v>
+        <v>79.97</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="L9">
-        <v>677082</v>
+        <v>679813</v>
       </c>
       <c r="M9">
-        <v>201795</v>
+        <v>121902</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F10">
-        <v>41.47</v>
+        <v>45.42</v>
       </c>
       <c r="G10" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H10">
-        <v>60.96</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I10" s="1">
         <v>1.52</v>
       </c>
       <c r="J10">
-        <v>63.03</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L10">
-        <v>95362</v>
+        <v>320891</v>
       </c>
       <c r="M10">
-        <v>203312</v>
+        <v>93846</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F11">
-        <v>32.11</v>
+        <v>57.33</v>
       </c>
       <c r="G11" s="1">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H11">
-        <v>45.6</v>
+        <v>82.56</v>
       </c>
       <c r="I11" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J11">
-        <v>48.49</v>
+        <v>87.14</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L11">
-        <v>130215</v>
+        <v>97750</v>
       </c>
       <c r="M11">
-        <v>203320</v>
+        <v>122991</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>72.89</v>
+        <v>32.8</v>
       </c>
       <c r="G12" s="1">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="H12">
-        <v>107.15</v>
+        <v>45.59</v>
       </c>
       <c r="I12" s="1">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J12">
-        <v>110.79</v>
+        <v>49.2</v>
       </c>
       <c r="K12" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L12">
-        <v>61420</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>144479</v>
+        <v>124637</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3">
-        <v>46195</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F13">
-        <v>57.49</v>
+        <v>277.75</v>
       </c>
       <c r="G13" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H13">
-        <v>84.51000000000001</v>
+        <v>399.96</v>
       </c>
       <c r="I13" s="1">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J13">
-        <v>87.38</v>
+        <v>419.4</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1055555</v>
       </c>
       <c r="M13">
-        <v>277407</v>
+        <v>82935</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3">
-        <v>46195</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F14">
-        <v>58.75</v>
+        <v>62.54</v>
       </c>
       <c r="G14" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H14">
-        <v>86.36</v>
+        <v>90.06</v>
       </c>
       <c r="I14" s="1">
         <v>1.52</v>
       </c>
       <c r="J14">
-        <v>89.3</v>
+        <v>95.06</v>
       </c>
       <c r="K14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L14">
-        <v>230213</v>
+        <v>221365</v>
       </c>
       <c r="M14">
-        <v>277469</v>
+        <v>82951</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F15">
-        <v>67.62</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G15" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H15">
-        <v>99.40000000000001</v>
+        <v>100.94</v>
       </c>
       <c r="I15" s="1">
         <v>1.52</v>
       </c>
       <c r="J15">
-        <v>102.78</v>
+        <v>106.55</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L15">
-        <v>319020</v>
+        <v>62381</v>
       </c>
       <c r="M15">
-        <v>90189</v>
+        <v>149547</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F16">
-        <v>80.36</v>
+        <v>74.63</v>
       </c>
       <c r="G16" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H16">
-        <v>118.13</v>
+        <v>107.47</v>
       </c>
       <c r="I16" s="1">
         <v>1.52</v>
       </c>
       <c r="J16">
-        <v>122.15</v>
+        <v>113.44</v>
       </c>
       <c r="K16" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L16">
-        <v>217140</v>
+        <v>189623</v>
       </c>
       <c r="M16">
-        <v>262250</v>
+        <v>149683</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="3">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F17">
-        <v>77.98999999999999</v>
+        <v>64.23</v>
       </c>
       <c r="G17" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H17">
-        <v>114.65</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="I17" s="1">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J17">
-        <v>118.54</v>
+        <v>98.27</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L17">
-        <v>188768</v>
+        <v>98262</v>
       </c>
       <c r="M17">
-        <v>118093</v>
+        <v>233042</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="3">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F18">
-        <v>68.87</v>
+        <v>62.2</v>
       </c>
       <c r="G18" s="1">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H18">
-        <v>101.24</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="I18" s="1">
         <v>1.52</v>
       </c>
       <c r="J18">
-        <v>104.68</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="L18">
-        <v>677517</v>
+        <v>321420</v>
       </c>
       <c r="M18">
-        <v>118135</v>
+        <v>94527</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="3">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F19">
-        <v>85.15000000000001</v>
+        <v>57.41</v>
       </c>
       <c r="G19" s="1">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="H19">
-        <v>151.57</v>
+        <v>82.67</v>
       </c>
       <c r="I19" s="1">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="J19">
-        <v>151.57</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="K19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L19">
-        <v>205792</v>
+        <v>231037</v>
       </c>
       <c r="M19">
-        <v>96127</v>
+        <v>281824</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="3">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>79.65000000000001</v>
+        <v>58.88</v>
       </c>
       <c r="G20" s="1">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H20">
-        <v>116.29</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I20" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J20">
-        <v>120.27</v>
+        <v>89.5</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L20">
-        <v>217880</v>
+        <v>221833</v>
       </c>
       <c r="M20">
-        <v>201172</v>
+        <v>132799</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="3">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F21">
-        <v>40.11</v>
+        <v>80.33</v>
       </c>
       <c r="G21" s="1">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H21">
-        <v>58.56</v>
+        <v>115.68</v>
       </c>
       <c r="I21" s="1">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J21">
-        <v>60.57</v>
+        <v>122.9</v>
       </c>
       <c r="K21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L21">
-        <v>677764</v>
+        <v>80500</v>
       </c>
       <c r="M21">
-        <v>118379</v>
+        <v>125190</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="3">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F22">
-        <v>52.35</v>
+        <v>51.16</v>
       </c>
       <c r="G22" s="1">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="H22">
-        <v>92.66</v>
+        <v>73.67</v>
       </c>
       <c r="I22" s="1">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="J22">
-        <v>92.66</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="K22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>145103</v>
+        <v>213448</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="3">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F23">
-        <v>64.90000000000001</v>
+        <v>73.56</v>
       </c>
       <c r="G23" s="1">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H23">
-        <v>94.75</v>
+        <v>105.93</v>
       </c>
       <c r="I23" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J23">
-        <v>98</v>
+        <v>111.81</v>
       </c>
       <c r="K23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L23">
-        <v>95930</v>
+        <v>207365</v>
       </c>
       <c r="M23">
-        <v>209636</v>
+        <v>133080</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="3">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F24">
-        <v>75.91</v>
+        <v>282.64</v>
       </c>
       <c r="G24" s="1">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H24">
-        <v>110.83</v>
+        <v>407</v>
       </c>
       <c r="I24" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J24">
-        <v>114.62</v>
+        <v>429.61</v>
       </c>
       <c r="K24" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>12072</v>
       </c>
       <c r="M24">
-        <v>278043</v>
+        <v>279300</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="3">
-        <v>46197</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F25">
-        <v>66.03</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="G25" s="1">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H25">
-        <v>96.40000000000001</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I25" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J25">
-        <v>99.70999999999999</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L25">
-        <v>25739</v>
+        <v>26336</v>
       </c>
       <c r="M25">
-        <v>278051</v>
+        <v>282090</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="3">
-        <v>46198</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F26">
-        <v>47.67</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="G26" s="1">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H26">
-        <v>69.59999999999999</v>
+        <v>104.06</v>
       </c>
       <c r="I26" s="1">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="J26">
-        <v>71.98</v>
+        <v>109.02</v>
       </c>
       <c r="K26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L26">
-        <v>319463</v>
+        <v>243164</v>
       </c>
       <c r="M26">
-        <v>90788</v>
+        <v>213977</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="3">
-        <v>46198</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F27">
-        <v>18.94</v>
+        <v>61.48</v>
       </c>
       <c r="G27" s="1">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H27">
-        <v>27.65</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="I27" s="1">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J27">
-        <v>28.6</v>
+        <v>95.91</v>
       </c>
       <c r="K27" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L27">
-        <v>96155</v>
+        <v>321997</v>
       </c>
       <c r="M27">
-        <v>204940</v>
+        <v>95748</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="3">
-        <v>46198</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F28">
-        <v>28.99</v>
+        <v>32.17</v>
       </c>
       <c r="G28" s="1">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="H28">
-        <v>42.33</v>
+        <v>44.72</v>
       </c>
       <c r="I28" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J28">
-        <v>43.77</v>
+        <v>47.93</v>
       </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>131246</v>
       </c>
       <c r="M28">
-        <v>278190</v>
+        <v>151612</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="3">
-        <v>46198</v>
+        <v>46217</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F29">
-        <v>74.68000000000001</v>
+        <v>60.86</v>
       </c>
       <c r="G29" s="1">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="H29">
-        <v>109.03</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I29" s="1">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="J29">
-        <v>115.01</v>
+        <v>94.94</v>
       </c>
       <c r="K29" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L29">
-        <v>218606</v>
+        <v>222415</v>
       </c>
       <c r="M29">
-        <v>291172</v>
+        <v>134785</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="3">
-        <v>46198</v>
+        <v>46217</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F30">
-        <v>27.34</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G30" s="1">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="H30">
-        <v>38.55</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="1">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J30">
-        <v>41.28</v>
+        <v>100.46</v>
       </c>
       <c r="K30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>680205</v>
       </c>
       <c r="M30">
-        <v>118762</v>
+        <v>125888</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="3">
-        <v>46198</v>
+        <v>46218</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F31">
-        <v>57.51</v>
+        <v>52.63</v>
       </c>
       <c r="G31" s="1">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="H31">
-        <v>83.95999999999999</v>
+        <v>80</v>
       </c>
       <c r="I31" s="1">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J31">
-        <v>86.84</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K31" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L31">
-        <v>242318</v>
+        <v>322465</v>
       </c>
       <c r="M31">
-        <v>118822</v>
+        <v>96290</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="3">
-        <v>46199</v>
+        <v>46218</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
         <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F32">
-        <v>66.76000000000001</v>
+        <v>46.64</v>
       </c>
       <c r="G32" s="1">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="H32">
-        <v>96.13</v>
+        <v>70.89</v>
       </c>
       <c r="I32" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J32">
-        <v>100.81</v>
+        <v>73.69</v>
       </c>
       <c r="K32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L32">
-        <v>678228</v>
+        <v>62704</v>
       </c>
       <c r="M32">
-        <v>119059</v>
+        <v>152176</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="3">
-        <v>46199</v>
+        <v>46218</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F33">
-        <v>73.02</v>
+        <v>61.24</v>
       </c>
       <c r="G33" s="1">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="H33">
-        <v>105.15</v>
+        <v>93.08</v>
       </c>
       <c r="I33" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J33">
-        <v>110.26</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="K33" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="L33">
-        <v>206473</v>
+        <v>81075</v>
       </c>
       <c r="M33">
-        <v>265014</v>
+        <v>283642</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="3">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F34">
-        <v>51.47</v>
+        <v>71.22</v>
       </c>
       <c r="G34" s="1">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H34">
-        <v>73.59999999999999</v>
+        <v>108.25</v>
       </c>
       <c r="I34" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J34">
-        <v>77.72</v>
+        <v>112.53</v>
       </c>
       <c r="K34" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L34">
-        <v>319890</v>
+        <v>190022</v>
       </c>
       <c r="M34">
-        <v>91829</v>
+        <v>152312</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="3">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F35">
-        <v>57.9</v>
+        <v>46.57</v>
       </c>
       <c r="G35" s="1">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H35">
-        <v>82.8</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="I35" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J35">
-        <v>87.43000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="K35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="L35">
-        <v>96762</v>
+        <v>243558</v>
       </c>
       <c r="M35">
-        <v>207551</v>
+        <v>217255</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="3">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F36">
-        <v>83.42</v>
+        <v>40</v>
       </c>
       <c r="G36" s="1">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H36">
-        <v>119.29</v>
+        <v>60.8</v>
       </c>
       <c r="I36" s="1">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="J36">
-        <v>128.47</v>
+        <v>63.2</v>
       </c>
       <c r="K36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L36">
-        <v>219460</v>
+        <v>207677</v>
       </c>
       <c r="M36">
-        <v>217563</v>
+        <v>279424</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="3">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F37">
-        <v>58.41</v>
+        <v>21.1</v>
       </c>
       <c r="G37" s="1">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H37">
-        <v>83.53</v>
+        <v>29.54</v>
       </c>
       <c r="I37" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J37">
-        <v>88.2</v>
+        <v>31.44</v>
       </c>
       <c r="K37" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L37">
-        <v>420935</v>
+        <v>299544</v>
       </c>
       <c r="M37">
-        <v>120652</v>
+        <v>279448</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="3">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F38">
-        <v>65.19</v>
+        <v>24.51</v>
       </c>
       <c r="G38" s="1">
-        <v>1.43</v>
+        <v>0.63</v>
       </c>
       <c r="H38">
-        <v>93.22</v>
+        <v>15.44</v>
       </c>
       <c r="I38" s="1">
-        <v>1.51</v>
+        <v>0.63</v>
       </c>
       <c r="J38">
-        <v>98.44</v>
+        <v>15.44</v>
       </c>
       <c r="K38" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="L38">
-        <v>61871</v>
+        <v>299544</v>
       </c>
       <c r="M38">
-        <v>146750</v>
+        <v>279448</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="3">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F39">
-        <v>20.59</v>
+        <v>60.14</v>
       </c>
       <c r="G39" s="1">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H39">
-        <v>29.44</v>
+        <v>91.41</v>
       </c>
       <c r="I39" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J39">
-        <v>31.09</v>
+        <v>95.02</v>
       </c>
       <c r="K39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L39">
-        <v>206682</v>
+        <v>223075</v>
       </c>
       <c r="M39">
-        <v>267831</v>
+        <v>211043</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="3">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F40">
-        <v>41.47</v>
+        <v>51.4</v>
       </c>
       <c r="G40" s="1">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="H40">
-        <v>59.3</v>
+        <v>78.13</v>
       </c>
       <c r="I40" s="1">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="J40">
-        <v>62.62</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K40" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L40">
-        <v>242587</v>
+        <v>231394</v>
       </c>
       <c r="M40">
-        <v>206910</v>
+        <v>283741</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="3">
-        <v>46203</v>
+        <v>46218</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41">
+        <v>14.57</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H41">
+        <v>20.4</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J41">
+        <v>21.71</v>
+      </c>
+      <c r="K41" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41">
+        <v>131384</v>
+      </c>
+      <c r="M41">
+        <v>152463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="7">
+        <v>2579.48</v>
+      </c>
+      <c r="C46" s="7">
+        <v>35</v>
+      </c>
+      <c r="D46" s="8">
+        <v>1.4561</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3755.87</v>
+      </c>
+      <c r="F46" s="7">
+        <v>3949.52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="7">
+        <v>100.64</v>
+      </c>
+      <c r="C47" s="7">
+        <v>4</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1.3936</v>
+      </c>
+      <c r="E47" s="7">
+        <v>140.25</v>
+      </c>
+      <c r="F47" s="7">
+        <v>150.28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="7">
+        <v>24.51</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0.6299</v>
+      </c>
+      <c r="E48" s="7">
+        <v>15.44</v>
+      </c>
+      <c r="F48" s="7">
+        <v>15.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="10">
+        <v>2704.63</v>
+      </c>
+      <c r="C49" s="10">
         <v>40</v>
       </c>
-      <c r="D41" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41">
-        <v>78.23999999999999</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H41">
-        <v>111.88</v>
-      </c>
-      <c r="I41" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J41">
-        <v>118.14</v>
-      </c>
-      <c r="K41" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41">
-        <v>189206</v>
-      </c>
-      <c r="M41">
-        <v>92302</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" t="s">
-        <v>56</v>
-      </c>
-      <c r="E42" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42">
-        <v>57.88</v>
-      </c>
-      <c r="G42" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H42">
-        <v>82.77</v>
-      </c>
-      <c r="I42" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J42">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="K42" t="s">
-        <v>105</v>
-      </c>
-      <c r="L42">
-        <v>230619</v>
-      </c>
-      <c r="M42">
-        <v>279623</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B43" t="s">
-        <v>27</v>
-      </c>
-      <c r="C43" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" t="s">
-        <v>62</v>
-      </c>
-      <c r="F43">
-        <v>361.6</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H43">
-        <v>517.09</v>
-      </c>
-      <c r="I43" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J43">
-        <v>546.02</v>
-      </c>
-      <c r="K43" t="s">
-        <v>106</v>
-      </c>
-      <c r="L43">
-        <v>10088</v>
-      </c>
-      <c r="M43">
-        <v>32671</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44">
-        <v>59.82</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H44">
-        <v>85.54000000000001</v>
-      </c>
-      <c r="I44" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J44">
-        <v>90.33</v>
-      </c>
-      <c r="K44" t="s">
-        <v>107</v>
-      </c>
-      <c r="L44">
-        <v>678664</v>
-      </c>
-      <c r="M44">
-        <v>208379</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" t="s">
-        <v>36</v>
-      </c>
-      <c r="D45" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45">
-        <v>21.76</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1.39</v>
-      </c>
-      <c r="H45">
-        <v>30.25</v>
-      </c>
-      <c r="I45" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J45">
-        <v>32.64</v>
-      </c>
-      <c r="K45" t="s">
-        <v>108</v>
-      </c>
-      <c r="L45">
-        <v>130629</v>
-      </c>
-      <c r="M45">
-        <v>146979</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46">
-        <v>28.61</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="H46">
-        <v>18.88</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J46">
-        <v>18.88</v>
-      </c>
-      <c r="K46" t="s">
-        <v>109</v>
-      </c>
-      <c r="L46">
-        <v>229030</v>
-      </c>
-      <c r="M46">
-        <v>268183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47">
-        <v>30.58</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1.39</v>
-      </c>
-      <c r="H47">
-        <v>42.51</v>
-      </c>
-      <c r="I47" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J47">
-        <v>45.87</v>
-      </c>
-      <c r="K47" t="s">
-        <v>109</v>
-      </c>
-      <c r="L47">
-        <v>229030</v>
-      </c>
-      <c r="M47">
-        <v>268183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="3">
-        <v>46203</v>
-      </c>
-      <c r="B48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48">
-        <v>59.26</v>
-      </c>
-      <c r="G48" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H48">
-        <v>84.73999999999999</v>
-      </c>
-      <c r="I48" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J48">
-        <v>89.48</v>
-      </c>
-      <c r="K48" t="s">
-        <v>110</v>
-      </c>
-      <c r="L48">
-        <v>220070</v>
-      </c>
-      <c r="M48">
-        <v>204145</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B53" s="7">
-        <v>2907.44</v>
-      </c>
-      <c r="C53" s="7">
-        <v>39</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1.4698</v>
-      </c>
-      <c r="E53" s="7">
-        <v>4273.37</v>
-      </c>
-      <c r="F53" s="7">
-        <v>4449.67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="7">
-        <v>196.02</v>
-      </c>
-      <c r="C54" s="7">
-        <v>3</v>
-      </c>
-      <c r="D54" s="8">
-        <v>1.8072</v>
-      </c>
-      <c r="E54" s="7">
-        <v>354.25</v>
-      </c>
-      <c r="F54" s="7">
-        <v>354.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="7">
-        <v>111.79</v>
-      </c>
-      <c r="C55" s="7">
-        <v>4</v>
-      </c>
-      <c r="D55" s="8">
-        <v>1.4036</v>
-      </c>
-      <c r="E55" s="7">
-        <v>156.91</v>
-      </c>
-      <c r="F55" s="7">
-        <v>168.28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="7">
-        <v>28.61</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1</v>
-      </c>
-      <c r="D56" s="8">
-        <v>0.6599</v>
-      </c>
-      <c r="E56" s="7">
-        <v>18.88</v>
-      </c>
-      <c r="F56" s="7">
-        <v>18.88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B57" s="10">
-        <v>3243.86</v>
-      </c>
-      <c r="C57" s="10">
-        <v>47</v>
-      </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="10">
-        <v>4803.41</v>
-      </c>
-      <c r="F57" s="10">
-        <v>4991.08</v>
+      <c r="D49" s="8"/>
+      <c r="E49" s="10">
+        <v>3911.56</v>
+      </c>
+      <c r="F49" s="10">
+        <v>4115.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A44:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="127">
   <si>
     <t>Дата</t>
   </si>
@@ -52,52 +52,58 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1195 243 Тракия Езеро</t>
-  </si>
-  <si>
-    <t>1156 Добрич бул. Добруджа</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1178 Русе, бул. България</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1196 Пазарджик Царица Йоанна</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1173 Ямбол</t>
-  </si>
-  <si>
-    <t>1927 Пирдоп</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1152 Бургас езеро</t>
-  </si>
-  <si>
-    <t>1139 София Ломско шосе</t>
-  </si>
-  <si>
-    <t>1103 Велико Търново изход</t>
-  </si>
-  <si>
-    <t>1112 София Резбарска</t>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Тракия Езеро</t>
+  </si>
+  <si>
+    <t>Добрич Добруджа</t>
+  </si>
+  <si>
+    <t>Русе България</t>
+  </si>
+  <si>
+    <t>Бургас</t>
+  </si>
+  <si>
+    <t>Пазарджик</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Долни Богров</t>
+  </si>
+  <si>
+    <t>Ямбол</t>
+  </si>
+  <si>
+    <t>Тракия</t>
+  </si>
+  <si>
+    <t>Пирдоп</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>София Ломско шосе</t>
+  </si>
+  <si>
+    <t>Бургас езеро</t>
+  </si>
+  <si>
+    <t>София Резбарска</t>
+  </si>
+  <si>
+    <t>В.Търново</t>
+  </si>
+  <si>
+    <t>Плевен Мизия</t>
+  </si>
+  <si>
+    <t>Сливен</t>
   </si>
   <si>
     <t>В5941ТН</t>
@@ -118,6 +124,9 @@
     <t>В9702ТА</t>
   </si>
   <si>
+    <t>B3018XK</t>
+  </si>
+  <si>
     <t>В4288ХА</t>
   </si>
   <si>
@@ -130,9 +139,15 @@
     <t>В7430ТМ</t>
   </si>
   <si>
+    <t>СВ5723НB</t>
+  </si>
+  <si>
     <t>В1052НН</t>
   </si>
   <si>
+    <t>В5982XK</t>
+  </si>
+  <si>
     <t>В6957НТ</t>
   </si>
   <si>
@@ -145,6 +160,9 @@
     <t>В0509ХА</t>
   </si>
   <si>
+    <t>В2573ХЕ</t>
+  </si>
+  <si>
     <t>78970155027720030</t>
   </si>
   <si>
@@ -163,6 +181,9 @@
     <t>78970155027720113</t>
   </si>
   <si>
+    <t>78970153027721439</t>
+  </si>
+  <si>
     <t>78970155027720162</t>
   </si>
   <si>
@@ -175,9 +196,15 @@
     <t>78970155027720147</t>
   </si>
   <si>
+    <t>78970152027720144</t>
+  </si>
+  <si>
     <t>78970155027720121</t>
   </si>
   <si>
+    <t>78970156027720822</t>
+  </si>
+  <si>
     <t>78970155027720089</t>
   </si>
   <si>
@@ -190,6 +217,9 @@
     <t>78970155027720063</t>
   </si>
   <si>
+    <t>78970151027720583</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
@@ -199,121 +229,154 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>13:49</t>
-  </si>
-  <si>
-    <t>04:38</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>11:38</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>10:06</t>
-  </si>
-  <si>
-    <t>04:43</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>14:17</t>
-  </si>
-  <si>
-    <t>10:43</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>14:53</t>
-  </si>
-  <si>
-    <t>15:44</t>
-  </si>
-  <si>
-    <t>11:52</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:12</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>04:59</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>05:01</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>13:21</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>15:27</t>
-  </si>
-  <si>
-    <t>15:37</t>
-  </si>
-  <si>
-    <t>16:33</t>
+    <t>2026-07-01 09:39:13</t>
+  </si>
+  <si>
+    <t>2026-07-01 13:49:33</t>
+  </si>
+  <si>
+    <t>2026-07-02 04:38:03</t>
+  </si>
+  <si>
+    <t>2026-07-02 09:00:06</t>
+  </si>
+  <si>
+    <t>2026-07-02 11:38:38</t>
+  </si>
+  <si>
+    <t>2026-07-02 12:21:03</t>
+  </si>
+  <si>
+    <t>2026-07-02 14:41:53</t>
+  </si>
+  <si>
+    <t>2026-07-03 10:06:59</t>
+  </si>
+  <si>
+    <t>2026-07-04 07:27:17</t>
+  </si>
+  <si>
+    <t>2026-07-06 04:42:15</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:26:33</t>
+  </si>
+  <si>
+    <t>2026-07-06 14:17:41</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:43:27</t>
+  </si>
+  <si>
+    <t>2026-07-07 11:56:50</t>
+  </si>
+  <si>
+    <t>2026-07-07 13:50:14</t>
+  </si>
+  <si>
+    <t>2026-07-08 08:09:42</t>
+  </si>
+  <si>
+    <t>2026-07-08 11:27:14</t>
+  </si>
+  <si>
+    <t>2026-07-08 11:34:50</t>
+  </si>
+  <si>
+    <t>2026-07-08 11:35:02</t>
+  </si>
+  <si>
+    <t>2026-07-08 12:39:10</t>
+  </si>
+  <si>
+    <t>2026-07-08 14:47:13</t>
+  </si>
+  <si>
+    <t>2026-07-08 14:54:24</t>
+  </si>
+  <si>
+    <t>2026-07-08 15:44:30</t>
+  </si>
+  <si>
+    <t>2026-07-08 16:22:42</t>
+  </si>
+  <si>
+    <t>2026-07-09 11:52:56</t>
+  </si>
+  <si>
+    <t>2026-07-09 12:05:56</t>
+  </si>
+  <si>
+    <t>2026-07-09 13:10:58</t>
+  </si>
+  <si>
+    <t>2026-07-09 13:22:11</t>
+  </si>
+  <si>
+    <t>2026-07-09 13:28:21</t>
+  </si>
+  <si>
+    <t>2026-07-10 09:16:29</t>
+  </si>
+  <si>
+    <t>2026-07-13 04:59:45</t>
+  </si>
+  <si>
+    <t>2026-07-13 10:08:02</t>
+  </si>
+  <si>
+    <t>2026-07-13 15:12:11</t>
+  </si>
+  <si>
+    <t>2026-07-14 09:21:02</t>
+  </si>
+  <si>
+    <t>2026-07-14 11:14:23</t>
+  </si>
+  <si>
+    <t>2026-07-15 05:01:28</t>
+  </si>
+  <si>
+    <t>2026-07-15 07:56:34</t>
+  </si>
+  <si>
+    <t>2026-07-15 09:07:38</t>
+  </si>
+  <si>
+    <t>2026-07-15 10:32:20</t>
+  </si>
+  <si>
+    <t>2026-07-15 11:37:58</t>
+  </si>
+  <si>
+    <t>2026-07-15 11:40:18</t>
+  </si>
+  <si>
+    <t>2026-07-15 13:21:32</t>
+  </si>
+  <si>
+    <t>2026-07-15 13:48:14</t>
+  </si>
+  <si>
+    <t>2026-07-15 14:18:25</t>
+  </si>
+  <si>
+    <t>2026-07-15 14:18:26</t>
+  </si>
+  <si>
+    <t>2026-07-15 15:02:55</t>
+  </si>
+  <si>
+    <t>2026-07-15 15:27:21</t>
+  </si>
+  <si>
+    <t>2026-07-15 15:36:52</t>
+  </si>
+  <si>
+    <t>2026-07-15 16:33:57</t>
+  </si>
+  <si>
+    <t>2026-07-15 17:16:44</t>
   </si>
   <si>
     <t>Общи литри по продукт / ФУУДС ТРЕЙД ЕООД</t>
@@ -733,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -746,12 +809,11 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -788,25 +850,22 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3">
         <v>46204</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F2">
         <v>68.37</v>
@@ -824,30 +883,27 @@
         <v>103.24</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L2">
         <v>79800</v>
       </c>
-      <c r="M2">
-        <v>207482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="3">
         <v>46204</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F3">
         <v>50.09</v>
@@ -865,30 +921,27 @@
         <v>77.14</v>
       </c>
       <c r="K3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="L3">
         <v>679000</v>
       </c>
-      <c r="M3">
-        <v>276852</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="3">
         <v>46205</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F4">
         <v>75.97</v>
@@ -906,30 +959,27 @@
         <v>114.71</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L4">
         <v>320497</v>
       </c>
-      <c r="M4">
-        <v>92835</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="3">
         <v>46205</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F5">
         <v>59.14</v>
@@ -947,30 +997,27 @@
         <v>89.3</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L5">
         <v>421300</v>
       </c>
-      <c r="M5">
-        <v>280171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="3">
         <v>46205</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F6">
         <v>65.19</v>
@@ -988,30 +1035,27 @@
         <v>98.44</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L6">
         <v>679451</v>
       </c>
-      <c r="M6">
-        <v>121746</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="3">
         <v>46205</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F7">
         <v>59.12</v>
@@ -1029,30 +1073,27 @@
         <v>89.27</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L7">
-        <v>175703</v>
-      </c>
-      <c r="M7">
-        <v>126738</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>97122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="3">
         <v>46205</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F8">
         <v>75.33</v>
@@ -1070,30 +1111,27 @@
         <v>113.75</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L8">
         <v>220850</v>
       </c>
-      <c r="M8">
-        <v>205003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="3">
         <v>46206</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F9">
         <v>52.96</v>
@@ -1111,426 +1149,393 @@
         <v>79.97</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L9">
         <v>679813</v>
       </c>
-      <c r="M9">
-        <v>121902</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="3">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F10">
-        <v>45.42</v>
+        <v>318.69</v>
       </c>
       <c r="G10" s="1">
         <v>1.44</v>
       </c>
       <c r="H10">
-        <v>65.40000000000001</v>
+        <v>458.91</v>
       </c>
       <c r="I10" s="1">
         <v>1.52</v>
       </c>
       <c r="J10">
-        <v>69.04000000000001</v>
+        <v>484.41</v>
       </c>
       <c r="K10" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L10">
-        <v>320891</v>
-      </c>
-      <c r="M10">
-        <v>93846</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="3">
         <v>46209</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F11">
-        <v>57.33</v>
+        <v>45.42</v>
       </c>
       <c r="G11" s="1">
         <v>1.44</v>
       </c>
       <c r="H11">
-        <v>82.56</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I11" s="1">
         <v>1.52</v>
       </c>
       <c r="J11">
-        <v>87.14</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L11">
-        <v>97750</v>
-      </c>
-      <c r="M11">
-        <v>122991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>320891</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="3">
         <v>46209</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F12">
+        <v>57.33</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H12">
+        <v>82.56</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J12">
+        <v>87.14</v>
+      </c>
+      <c r="K12" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12">
+        <v>97750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13">
         <v>32.8</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <v>1.39</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>45.59</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I13" s="1">
         <v>1.5</v>
       </c>
-      <c r="J12">
+      <c r="J13">
         <v>49.2</v>
       </c>
-      <c r="K12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12">
+      <c r="K13" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13">
         <v>0</v>
       </c>
-      <c r="M12">
-        <v>124637</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13">
-        <v>277.75</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H13">
-        <v>399.96</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J13">
-        <v>419.4</v>
-      </c>
-      <c r="K13" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13">
-        <v>1055555</v>
-      </c>
-      <c r="M13">
-        <v>82935</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="3">
         <v>46210</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F14">
-        <v>62.54</v>
+        <v>277.75</v>
       </c>
       <c r="G14" s="1">
         <v>1.44</v>
       </c>
       <c r="H14">
-        <v>90.06</v>
+        <v>399.96</v>
       </c>
       <c r="I14" s="1">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J14">
-        <v>95.06</v>
+        <v>419.4</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L14">
-        <v>221365</v>
-      </c>
-      <c r="M14">
-        <v>82951</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>1055555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="3">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F15">
-        <v>70.09999999999999</v>
+        <v>334.24</v>
       </c>
       <c r="G15" s="1">
         <v>1.44</v>
       </c>
       <c r="H15">
-        <v>100.94</v>
+        <v>481.31</v>
       </c>
       <c r="I15" s="1">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="J15">
-        <v>106.55</v>
+        <v>521.41</v>
       </c>
       <c r="K15" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>62381</v>
-      </c>
-      <c r="M15">
-        <v>149547</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>839408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="3">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F16">
-        <v>74.63</v>
+        <v>62.54</v>
       </c>
       <c r="G16" s="1">
         <v>1.44</v>
       </c>
       <c r="H16">
-        <v>107.47</v>
+        <v>90.06</v>
       </c>
       <c r="I16" s="1">
         <v>1.52</v>
       </c>
       <c r="J16">
-        <v>113.44</v>
+        <v>95.06</v>
       </c>
       <c r="K16" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L16">
-        <v>189623</v>
-      </c>
-      <c r="M16">
-        <v>149683</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>221365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="3">
         <v>46211</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F17">
-        <v>64.23</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G17" s="1">
         <v>1.44</v>
       </c>
       <c r="H17">
-        <v>92.48999999999999</v>
+        <v>100.94</v>
       </c>
       <c r="I17" s="1">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J17">
-        <v>98.27</v>
+        <v>106.55</v>
       </c>
       <c r="K17" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L17">
-        <v>98262</v>
-      </c>
-      <c r="M17">
-        <v>233042</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>62381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="3">
         <v>46211</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>62.2</v>
+        <v>74.63</v>
       </c>
       <c r="G18" s="1">
         <v>1.44</v>
       </c>
       <c r="H18">
-        <v>89.56999999999999</v>
+        <v>107.47</v>
       </c>
       <c r="I18" s="1">
         <v>1.52</v>
       </c>
       <c r="J18">
-        <v>94.54000000000001</v>
+        <v>113.44</v>
       </c>
       <c r="K18" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="L18">
-        <v>321420</v>
-      </c>
-      <c r="M18">
-        <v>94527</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>189623</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="3">
         <v>46211</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>57.41</v>
+        <v>77.2</v>
       </c>
       <c r="G19" s="1">
         <v>1.44</v>
       </c>
       <c r="H19">
-        <v>82.67</v>
+        <v>111.17</v>
       </c>
       <c r="I19" s="1">
         <v>1.52</v>
       </c>
       <c r="J19">
-        <v>87.26000000000001</v>
+        <v>117.34</v>
       </c>
       <c r="K19" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="L19">
-        <v>231037</v>
-      </c>
-      <c r="M19">
-        <v>281824</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>247381</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="3">
         <v>46211</v>
       </c>
@@ -1538,575 +1543,533 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F20">
-        <v>58.88</v>
+        <v>64.23</v>
       </c>
       <c r="G20" s="1">
         <v>1.44</v>
       </c>
       <c r="H20">
-        <v>84.79000000000001</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="I20" s="1">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J20">
-        <v>89.5</v>
+        <v>98.27</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L20">
-        <v>221833</v>
-      </c>
-      <c r="M20">
-        <v>132799</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>98262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="3">
         <v>46211</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F21">
-        <v>80.33</v>
+        <v>62.2</v>
       </c>
       <c r="G21" s="1">
         <v>1.44</v>
       </c>
       <c r="H21">
-        <v>115.68</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="I21" s="1">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J21">
-        <v>122.9</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="K21" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L21">
-        <v>80500</v>
-      </c>
-      <c r="M21">
-        <v>125190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>321420</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="3">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F22">
-        <v>51.16</v>
+        <v>57.41</v>
       </c>
       <c r="G22" s="1">
         <v>1.44</v>
       </c>
       <c r="H22">
-        <v>73.67</v>
+        <v>82.67</v>
       </c>
       <c r="I22" s="1">
         <v>1.52</v>
       </c>
       <c r="J22">
-        <v>77.76000000000001</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="K22" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>213448</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>231037</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="3">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
         <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F23">
-        <v>73.56</v>
+        <v>58.88</v>
       </c>
       <c r="G23" s="1">
         <v>1.44</v>
       </c>
       <c r="H23">
-        <v>105.93</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="I23" s="1">
         <v>1.52</v>
       </c>
       <c r="J23">
-        <v>111.81</v>
+        <v>89.5</v>
       </c>
       <c r="K23" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L23">
-        <v>207365</v>
-      </c>
-      <c r="M23">
-        <v>133080</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>221833</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="3">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F24">
-        <v>282.64</v>
+        <v>80.33</v>
       </c>
       <c r="G24" s="1">
         <v>1.44</v>
       </c>
       <c r="H24">
+        <v>115.68</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="J24">
+        <v>122.9</v>
+      </c>
+      <c r="K24" t="s">
+        <v>93</v>
+      </c>
+      <c r="L24">
+        <v>80500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="3">
+        <v>46211</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25">
+        <v>53.02</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="H25">
+        <v>73.7</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J25">
+        <v>79</v>
+      </c>
+      <c r="K25" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26">
+        <v>51.16</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H26">
+        <v>73.67</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J26">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="K26" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27">
+        <v>73.56</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H27">
+        <v>105.93</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J27">
+        <v>111.81</v>
+      </c>
+      <c r="K27" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27">
+        <v>207365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28">
+        <v>282.64</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H28">
         <v>407</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I28" s="1">
         <v>1.52</v>
       </c>
-      <c r="J24">
+      <c r="J28">
         <v>429.61</v>
       </c>
-      <c r="K24" t="s">
-        <v>83</v>
-      </c>
-      <c r="L24">
+      <c r="K28" t="s">
+        <v>97</v>
+      </c>
+      <c r="L28">
         <v>12072</v>
       </c>
-      <c r="M24">
-        <v>279300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="3">
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3">
         <v>46212</v>
       </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25">
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29">
         <v>67.76000000000001</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G29" s="1">
         <v>1.44</v>
       </c>
-      <c r="H25">
+      <c r="H29">
         <v>97.56999999999999</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I29" s="1">
         <v>1.52</v>
       </c>
-      <c r="J25">
+      <c r="J29">
         <v>103</v>
       </c>
-      <c r="K25" t="s">
-        <v>84</v>
-      </c>
-      <c r="L25">
+      <c r="K29" t="s">
+        <v>98</v>
+      </c>
+      <c r="L29">
         <v>26336</v>
       </c>
-      <c r="M25">
-        <v>282090</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="3">
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30">
+        <v>68.81999999999999</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="H30">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J30">
+        <v>104.61</v>
+      </c>
+      <c r="K30" t="s">
+        <v>99</v>
+      </c>
+      <c r="L30">
+        <v>247960</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3">
         <v>46213</v>
       </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26">
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31">
         <v>70.79000000000001</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G31" s="1">
         <v>1.47</v>
       </c>
-      <c r="H26">
+      <c r="H31">
         <v>104.06</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I31" s="1">
         <v>1.54</v>
       </c>
-      <c r="J26">
+      <c r="J31">
         <v>109.02</v>
       </c>
-      <c r="K26" t="s">
-        <v>85</v>
-      </c>
-      <c r="L26">
+      <c r="K31" t="s">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>243164</v>
       </c>
-      <c r="M26">
-        <v>213977</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="3">
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3">
         <v>46216</v>
       </c>
-      <c r="B27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27">
-        <v>61.48</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H27">
-        <v>90.98999999999999</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J27">
-        <v>95.91</v>
-      </c>
-      <c r="K27" t="s">
-        <v>86</v>
-      </c>
-      <c r="L27">
-        <v>321997</v>
-      </c>
-      <c r="M27">
-        <v>95748</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28">
-        <v>32.17</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1.39</v>
-      </c>
-      <c r="H28">
-        <v>44.72</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J28">
-        <v>47.93</v>
-      </c>
-      <c r="K28" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28">
-        <v>131246</v>
-      </c>
-      <c r="M28">
-        <v>151612</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29">
-        <v>60.86</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H29">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J29">
-        <v>94.94</v>
-      </c>
-      <c r="K29" t="s">
-        <v>88</v>
-      </c>
-      <c r="L29">
-        <v>222415</v>
-      </c>
-      <c r="M29">
-        <v>134785</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H30">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J30">
-        <v>100.46</v>
-      </c>
-      <c r="K30" t="s">
-        <v>89</v>
-      </c>
-      <c r="L30">
-        <v>680205</v>
-      </c>
-      <c r="M30">
-        <v>125888</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B31" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31">
-        <v>52.63</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H31">
-        <v>80</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J31">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="K31" t="s">
-        <v>90</v>
-      </c>
-      <c r="L31">
-        <v>322465</v>
-      </c>
-      <c r="M31">
-        <v>96290</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="3">
-        <v>46218</v>
-      </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
         <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>46.64</v>
+        <v>61.48</v>
       </c>
       <c r="G32" s="1">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H32">
-        <v>70.89</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="I32" s="1">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J32">
-        <v>73.69</v>
+        <v>95.91</v>
       </c>
       <c r="K32" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="L32">
-        <v>62704</v>
-      </c>
-      <c r="M32">
-        <v>152176</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>321997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="3">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F33">
-        <v>61.24</v>
+        <v>63.65</v>
       </c>
       <c r="G33" s="1">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H33">
-        <v>93.08</v>
+        <v>94.2</v>
       </c>
       <c r="I33" s="1">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J33">
-        <v>96.76000000000001</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="K33" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L33">
-        <v>81075</v>
-      </c>
-      <c r="M33">
-        <v>283642</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>248451</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="3">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
@@ -2115,434 +2078,790 @@
         <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F34">
-        <v>71.22</v>
+        <v>32.17</v>
       </c>
       <c r="G34" s="1">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="H34">
-        <v>108.25</v>
+        <v>44.72</v>
       </c>
       <c r="I34" s="1">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="J34">
-        <v>112.53</v>
+        <v>47.93</v>
       </c>
       <c r="K34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="L34">
-        <v>190022</v>
-      </c>
-      <c r="M34">
-        <v>152312</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>131246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="3">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F35">
-        <v>46.57</v>
+        <v>60.86</v>
       </c>
       <c r="G35" s="1">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H35">
-        <v>70.79000000000001</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I35" s="1">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J35">
-        <v>73.58</v>
+        <v>94.94</v>
       </c>
       <c r="K35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="L35">
-        <v>243558</v>
-      </c>
-      <c r="M35">
-        <v>217255</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>222415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="3">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F36">
-        <v>40</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G36" s="1">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H36">
-        <v>60.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I36" s="1">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J36">
-        <v>63.2</v>
+        <v>100.46</v>
       </c>
       <c r="K36" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L36">
-        <v>207677</v>
-      </c>
-      <c r="M36">
-        <v>279424</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>680205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="3">
         <v>46218</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F37">
-        <v>21.1</v>
+        <v>52.63</v>
       </c>
       <c r="G37" s="1">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="H37">
-        <v>29.54</v>
+        <v>80</v>
       </c>
       <c r="I37" s="1">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="J37">
-        <v>31.44</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K37" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L37">
-        <v>299544</v>
-      </c>
-      <c r="M37">
-        <v>279448</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>322465</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" s="3">
         <v>46218</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F38">
-        <v>24.51</v>
+        <v>46.64</v>
       </c>
       <c r="G38" s="1">
-        <v>0.63</v>
+        <v>1.52</v>
       </c>
       <c r="H38">
-        <v>15.44</v>
+        <v>70.89</v>
       </c>
       <c r="I38" s="1">
-        <v>0.63</v>
+        <v>1.58</v>
       </c>
       <c r="J38">
-        <v>15.44</v>
+        <v>73.69</v>
       </c>
       <c r="K38" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="L38">
-        <v>299544</v>
-      </c>
-      <c r="M38">
-        <v>279448</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>62704</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="3">
         <v>46218</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F39">
-        <v>60.14</v>
+        <v>62.61</v>
       </c>
       <c r="G39" s="1">
         <v>1.52</v>
       </c>
       <c r="H39">
-        <v>91.41</v>
+        <v>95.17</v>
       </c>
       <c r="I39" s="1">
         <v>1.58</v>
       </c>
       <c r="J39">
-        <v>95.02</v>
+        <v>98.92</v>
       </c>
       <c r="K39" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="L39">
-        <v>223075</v>
-      </c>
-      <c r="M39">
-        <v>211043</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>248988</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" s="3">
         <v>46218</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F40">
-        <v>51.4</v>
+        <v>61.24</v>
       </c>
       <c r="G40" s="1">
         <v>1.52</v>
       </c>
       <c r="H40">
-        <v>78.13</v>
+        <v>93.08</v>
       </c>
       <c r="I40" s="1">
         <v>1.58</v>
       </c>
       <c r="J40">
-        <v>81.20999999999999</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="K40" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L40">
-        <v>231394</v>
-      </c>
-      <c r="M40">
-        <v>283741</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>81075</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="3">
         <v>46218</v>
       </c>
       <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41">
+        <v>249.73</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H41">
+        <v>379.59</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J41">
+        <v>394.57</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B42" t="s">
         <v>23</v>
       </c>
-      <c r="C41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
         <v>59</v>
       </c>
-      <c r="F41">
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42">
+        <v>71.22</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H42">
+        <v>108.25</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J42">
+        <v>112.53</v>
+      </c>
+      <c r="K42" t="s">
+        <v>111</v>
+      </c>
+      <c r="L42">
+        <v>190022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43">
+        <v>46.57</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H43">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J43">
+        <v>73.58</v>
+      </c>
+      <c r="K43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L43">
+        <v>243558</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44">
+        <v>40</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H44">
+        <v>60.8</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J44">
+        <v>63.2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>113</v>
+      </c>
+      <c r="L44">
+        <v>207677</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45">
+        <v>21.1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H45">
+        <v>29.54</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J45">
+        <v>31.44</v>
+      </c>
+      <c r="K45" t="s">
+        <v>114</v>
+      </c>
+      <c r="L45">
+        <v>299544</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46">
+        <v>24.51</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="H46">
+        <v>15.44</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="J46">
+        <v>15.44</v>
+      </c>
+      <c r="K46" t="s">
+        <v>115</v>
+      </c>
+      <c r="L46">
+        <v>299544</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47">
+        <v>4.01</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H47">
+        <v>5.61</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J47">
+        <v>5.97</v>
+      </c>
+      <c r="K47" t="s">
+        <v>116</v>
+      </c>
+      <c r="L47">
+        <v>237382</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48">
+        <v>60.14</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H48">
+        <v>91.41</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J48">
+        <v>95.02</v>
+      </c>
+      <c r="K48" t="s">
+        <v>117</v>
+      </c>
+      <c r="L48">
+        <v>223075</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" t="s">
+        <v>68</v>
+      </c>
+      <c r="F49">
+        <v>51.4</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H49">
+        <v>78.13</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J49">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="K49" t="s">
+        <v>118</v>
+      </c>
+      <c r="L49">
+        <v>231394</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50">
         <v>14.57</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G50" s="1">
         <v>1.4</v>
       </c>
-      <c r="H41">
+      <c r="H50">
         <v>20.4</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I50" s="1">
         <v>1.49</v>
       </c>
-      <c r="J41">
+      <c r="J50">
         <v>21.71</v>
       </c>
-      <c r="K41" t="s">
-        <v>99</v>
-      </c>
-      <c r="L41">
+      <c r="K50" t="s">
+        <v>119</v>
+      </c>
+      <c r="L50">
         <v>131384</v>
       </c>
-      <c r="M41">
-        <v>152463</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-    </row>
-    <row r="45" spans="1:13">
-      <c r="A45" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" s="5" t="s">
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51">
+        <v>50.34</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H51">
+        <v>70.48</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J51">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="K51" t="s">
+        <v>120</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
-      <c r="A46" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="7">
-        <v>2579.48</v>
-      </c>
-      <c r="C46" s="7">
-        <v>35</v>
-      </c>
-      <c r="D46" s="8">
-        <v>1.4561</v>
-      </c>
-      <c r="E46" s="7">
-        <v>3755.87</v>
-      </c>
-      <c r="F46" s="7">
-        <v>3949.52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="7">
-        <v>100.64</v>
-      </c>
-      <c r="C47" s="7">
-        <v>4</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1.3936</v>
-      </c>
-      <c r="E47" s="7">
-        <v>140.25</v>
-      </c>
-      <c r="F47" s="7">
-        <v>150.28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="A48" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48" s="7">
+    <row r="56" spans="1:12">
+      <c r="A56" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="7">
+        <v>3754.42</v>
+      </c>
+      <c r="C56" s="7">
+        <v>42</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1.4584</v>
+      </c>
+      <c r="E56" s="7">
+        <v>5475.32</v>
+      </c>
+      <c r="F56" s="7">
+        <v>5770.07</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="7">
+        <v>208.01</v>
+      </c>
+      <c r="C57" s="7">
+        <v>7</v>
+      </c>
+      <c r="D57" s="8">
+        <v>1.3944</v>
+      </c>
+      <c r="E57" s="7">
+        <v>290.04</v>
+      </c>
+      <c r="F57" s="7">
+        <v>310.26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="7">
         <v>24.51</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C58" s="7">
         <v>1</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D58" s="8">
         <v>0.6299</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E58" s="7">
         <v>15.44</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F58" s="7">
         <v>15.44</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" s="10">
-        <v>2704.63</v>
-      </c>
-      <c r="C49" s="10">
-        <v>40</v>
-      </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="10">
-        <v>3911.56</v>
-      </c>
-      <c r="F49" s="10">
-        <v>4115.24</v>
+    <row r="59" spans="1:12">
+      <c r="A59" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="10">
+        <v>3986.94</v>
+      </c>
+      <c r="C59" s="10">
+        <v>50</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="10">
+        <v>5780.8</v>
+      </c>
+      <c r="F59" s="10">
+        <v>6095.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A54:F54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -596,7 +596,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3600,7 +3600,7 @@
         <v>46</v>
       </c>
       <c r="D63" s="8">
-        <v>1.6289</v>
+        <v>1.628897</v>
       </c>
       <c r="E63" s="7">
         <v>7280.99</v>
@@ -3620,7 +3620,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="8">
-        <v>1.4689</v>
+        <v>1.468928</v>
       </c>
       <c r="E64" s="7">
         <v>469.91</v>
@@ -3640,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="8">
-        <v>1.91</v>
+        <v>1.909985</v>
       </c>
       <c r="E65" s="7">
         <v>118.4</v>
@@ -3660,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="8">
-        <v>0.6401</v>
+        <v>0.640073</v>
       </c>
       <c r="E66" s="7">
         <v>10.51</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="192">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -988,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1001,13 +1004,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1050,2518 +1053,2692 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2">
-        <v>318.02</v>
+        <v>318.019</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>486.57</v>
+        <v>1.529</v>
       </c>
       <c r="J2">
+        <v>486.251051</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
-        <v>512.01</v>
-      </c>
-      <c r="L2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>512.01059</v>
+      </c>
+      <c r="M2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2">
         <v>841060</v>
       </c>
-      <c r="N2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3">
-        <v>321.73</v>
+        <v>321.731</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>492.25</v>
+        <v>1.529</v>
       </c>
       <c r="J3">
+        <v>491.926699</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.6</v>
       </c>
-      <c r="K3" s="1">
-        <v>514.77</v>
-      </c>
-      <c r="L3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>514.7696</v>
+      </c>
+      <c r="M3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4">
-        <v>81.2</v>
+        <v>81.199</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I4" s="1">
-        <v>124.24</v>
+        <v>1.529</v>
       </c>
       <c r="J4">
+        <v>124.153271</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.61</v>
       </c>
-      <c r="K4" s="1">
-        <v>130.73</v>
-      </c>
-      <c r="L4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>130.73039</v>
+      </c>
+      <c r="M4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4">
         <v>249703</v>
       </c>
-      <c r="N4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5">
-        <v>49.78</v>
+        <v>49.783</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I5" s="1">
-        <v>76.16</v>
+        <v>1.529</v>
       </c>
       <c r="J5">
+        <v>76.118207</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.61</v>
       </c>
-      <c r="K5" s="1">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>80.15063000000001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5">
         <v>422109</v>
       </c>
-      <c r="N5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>67.70999999999999</v>
+        <v>67.712</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I6" s="1">
-        <v>103.6</v>
+        <v>1.529</v>
       </c>
       <c r="J6">
+        <v>103.531648</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.63</v>
       </c>
-      <c r="K6" s="1">
-        <v>110.37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>110.37056</v>
+      </c>
+      <c r="M6" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6">
         <v>323048</v>
       </c>
-      <c r="N6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7">
-        <v>55.51</v>
+        <v>55.509</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7">
-        <v>1.53</v>
+        <v>1.499</v>
       </c>
       <c r="I7" s="1">
-        <v>84.93000000000001</v>
+        <v>1.529</v>
       </c>
       <c r="J7">
+        <v>84.873261</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.63</v>
       </c>
-      <c r="K7" s="1">
-        <v>90.48</v>
-      </c>
-      <c r="L7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>90.47967</v>
+      </c>
+      <c r="M7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7">
         <v>223627</v>
       </c>
-      <c r="N7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46221</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>57.57</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8">
-        <v>1.56</v>
+        <v>1.528</v>
       </c>
       <c r="I8" s="1">
-        <v>89.81</v>
+        <v>1.558</v>
       </c>
       <c r="J8">
+        <v>89.69405999999999</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.65</v>
       </c>
-      <c r="K8" s="1">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="L8" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>94.9905</v>
+      </c>
+      <c r="M8" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46221</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F9">
         <v>61.99</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>1.91</v>
       </c>
       <c r="I9" s="1">
-        <v>118.4</v>
+        <v>1.91</v>
       </c>
       <c r="J9">
+        <v>118.4009</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.91</v>
       </c>
-      <c r="K9" s="1">
-        <v>118.4</v>
-      </c>
-      <c r="L9" t="s">
-        <v>81</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>118.4009</v>
+      </c>
+      <c r="M9" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F10">
-        <v>27.7</v>
+        <v>27.699</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10">
-        <v>1.43</v>
+        <v>1.389</v>
       </c>
       <c r="I10" s="1">
-        <v>39.61</v>
+        <v>1.429</v>
       </c>
       <c r="J10">
+        <v>39.581871</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.53</v>
       </c>
-      <c r="K10" s="1">
-        <v>42.38</v>
-      </c>
-      <c r="L10" t="s">
-        <v>82</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>42.37947</v>
+      </c>
+      <c r="M10" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46224</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F11">
-        <v>350.51</v>
+        <v>350.509</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H11">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I11" s="1">
-        <v>557.3099999999999</v>
+        <v>1.594</v>
       </c>
       <c r="J11">
+        <v>558.711346</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.69</v>
       </c>
-      <c r="K11" s="1">
-        <v>592.36</v>
-      </c>
-      <c r="L11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>592.3602100000001</v>
+      </c>
+      <c r="M11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46224</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12">
-        <v>70.48999999999999</v>
+        <v>70.488</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H12">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I12" s="1">
-        <v>112.08</v>
+        <v>1.594</v>
       </c>
       <c r="J12">
+        <v>112.357872</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.66</v>
       </c>
-      <c r="K12" s="1">
-        <v>117.01</v>
-      </c>
-      <c r="L12" t="s">
-        <v>84</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>117.01008</v>
+      </c>
+      <c r="M12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12">
         <v>323603</v>
       </c>
-      <c r="N12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46224</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13">
-        <v>50.71</v>
+        <v>50.714</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I13" s="1">
-        <v>80.63</v>
+        <v>1.594</v>
       </c>
       <c r="J13">
+        <v>80.838116</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.68</v>
       </c>
-      <c r="K13" s="1">
-        <v>85.19</v>
-      </c>
-      <c r="L13" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>85.19952000000001</v>
+      </c>
+      <c r="M13" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13">
         <v>224123</v>
       </c>
-      <c r="N13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46224</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <v>76.03</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H14">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I14" s="1">
-        <v>120.89</v>
+        <v>1.594</v>
       </c>
       <c r="J14">
+        <v>121.19182</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.68</v>
       </c>
-      <c r="K14" s="1">
-        <v>127.73</v>
-      </c>
-      <c r="L14" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>127.7304</v>
+      </c>
+      <c r="M14" t="s">
+        <v>87</v>
+      </c>
+      <c r="N14">
         <v>81677</v>
       </c>
-      <c r="N14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46224</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15">
-        <v>56.07</v>
+        <v>56.071</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15">
-        <v>1.59</v>
+        <v>1.564</v>
       </c>
       <c r="I15" s="1">
-        <v>89.15000000000001</v>
+        <v>1.594</v>
       </c>
       <c r="J15">
+        <v>89.377174</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.68</v>
       </c>
-      <c r="K15" s="1">
-        <v>94.2</v>
-      </c>
-      <c r="L15" t="s">
-        <v>87</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>94.19928</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46225</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16">
-        <v>53.8</v>
+        <v>53.799</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I16" s="1">
-        <v>77.47</v>
+        <v>1.441</v>
       </c>
       <c r="J16">
+        <v>77.524359</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.54</v>
       </c>
-      <c r="K16" s="1">
-        <v>82.84999999999999</v>
-      </c>
-      <c r="L16" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>82.85046</v>
+      </c>
+      <c r="M16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46225</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>87.63</v>
+        <v>87.627</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I17" s="1">
-        <v>141.96</v>
+        <v>1.618</v>
       </c>
       <c r="J17">
+        <v>141.780486</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.69</v>
       </c>
-      <c r="K17" s="1">
-        <v>148.09</v>
-      </c>
-      <c r="L17" t="s">
-        <v>89</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>148.08963</v>
+      </c>
+      <c r="M17" t="s">
+        <v>90</v>
+      </c>
+      <c r="N17">
         <v>208372</v>
       </c>
-      <c r="N17" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46225</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18">
-        <v>320.59</v>
+        <v>320.588</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I18" s="1">
-        <v>519.36</v>
+        <v>1.618</v>
       </c>
       <c r="J18">
+        <v>518.711384</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.7</v>
       </c>
-      <c r="K18" s="1">
-        <v>545</v>
-      </c>
-      <c r="L18" t="s">
-        <v>90</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>544.9996</v>
+      </c>
+      <c r="M18" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18">
         <v>842085</v>
       </c>
-      <c r="N18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19">
-        <v>51.45</v>
+        <v>51.448</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I19" s="1">
-        <v>83.34999999999999</v>
+        <v>1.618</v>
       </c>
       <c r="J19">
+        <v>83.242864</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.72</v>
       </c>
-      <c r="K19" s="1">
-        <v>88.48999999999999</v>
-      </c>
-      <c r="L19" t="s">
-        <v>91</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="1">
+        <v>88.49056</v>
+      </c>
+      <c r="M19" t="s">
+        <v>92</v>
+      </c>
+      <c r="N19">
         <v>224607</v>
       </c>
-      <c r="N19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F20">
-        <v>74.91</v>
+        <v>74.911</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H20">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I20" s="1">
-        <v>121.35</v>
+        <v>1.618</v>
       </c>
       <c r="J20">
+        <v>121.205998</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.69</v>
       </c>
-      <c r="K20" s="1">
-        <v>126.6</v>
-      </c>
-      <c r="L20" t="s">
-        <v>92</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>126.59959</v>
+      </c>
+      <c r="M20" t="s">
+        <v>93</v>
+      </c>
+      <c r="N20">
         <v>250330</v>
       </c>
-      <c r="N20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21">
-        <v>75.44</v>
+        <v>75.441</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H21">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I21" s="1">
-        <v>122.21</v>
+        <v>1.618</v>
       </c>
       <c r="J21">
+        <v>122.063538</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.7</v>
       </c>
-      <c r="K21" s="1">
-        <v>128.25</v>
-      </c>
-      <c r="L21" t="s">
-        <v>93</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="1">
+        <v>128.2497</v>
+      </c>
+      <c r="M21" t="s">
+        <v>94</v>
+      </c>
+      <c r="N21">
         <v>190435</v>
       </c>
-      <c r="N21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22">
-        <v>66.56999999999999</v>
+        <v>66.56699999999999</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I22" s="1">
-        <v>107.84</v>
+        <v>1.618</v>
       </c>
       <c r="J22">
+        <v>107.705406</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.71</v>
       </c>
-      <c r="K22" s="1">
-        <v>113.83</v>
-      </c>
-      <c r="L22" t="s">
-        <v>94</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="1">
+        <v>113.82957</v>
+      </c>
+      <c r="M22" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22">
         <v>680680</v>
       </c>
-      <c r="N22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46226</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23">
-        <v>68.27</v>
+        <v>68.274</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I23" s="1">
-        <v>110.6</v>
+        <v>1.618</v>
       </c>
       <c r="J23">
+        <v>110.467332</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.68</v>
       </c>
-      <c r="K23" s="1">
-        <v>114.69</v>
-      </c>
-      <c r="L23" t="s">
-        <v>95</v>
-      </c>
-      <c r="M23">
+      <c r="L23" s="1">
+        <v>114.70032</v>
+      </c>
+      <c r="M23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23">
         <v>324195</v>
       </c>
-      <c r="N23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46226</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F24">
-        <v>53.64</v>
+        <v>53.639</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24">
-        <v>1.62</v>
+        <v>1.588</v>
       </c>
       <c r="I24" s="1">
-        <v>86.90000000000001</v>
+        <v>1.618</v>
       </c>
       <c r="J24">
+        <v>86.787902</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.69</v>
       </c>
-      <c r="K24" s="1">
-        <v>90.65000000000001</v>
-      </c>
-      <c r="L24" t="s">
-        <v>96</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>90.64991000000001</v>
+      </c>
+      <c r="M24" t="s">
+        <v>97</v>
+      </c>
+      <c r="N24">
         <v>0</v>
       </c>
-      <c r="N24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25">
-        <v>37.6</v>
+        <v>37.597</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I25" s="1">
-        <v>54.14</v>
+        <v>1.441</v>
       </c>
       <c r="J25">
+        <v>54.177277</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.54</v>
       </c>
-      <c r="K25" s="1">
-        <v>57.9</v>
-      </c>
-      <c r="L25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="1">
+        <v>57.89938</v>
+      </c>
+      <c r="M25" t="s">
+        <v>98</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46227</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26">
-        <v>82.88</v>
+        <v>82.878</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H26">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I26" s="1">
-        <v>136.75</v>
+        <v>1.649</v>
       </c>
       <c r="J26">
+        <v>136.665822</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.72</v>
       </c>
-      <c r="K26" s="1">
-        <v>142.55</v>
-      </c>
-      <c r="L26" t="s">
-        <v>98</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="1">
+        <v>142.55016</v>
+      </c>
+      <c r="M26" t="s">
+        <v>99</v>
+      </c>
+      <c r="N26">
         <v>251005</v>
       </c>
-      <c r="N26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46227</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27">
-        <v>61.85</v>
+        <v>61.849</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H27">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I27" s="1">
-        <v>102.05</v>
+        <v>1.649</v>
       </c>
       <c r="J27">
+        <v>101.989001</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.72</v>
       </c>
-      <c r="K27" s="1">
-        <v>106.38</v>
-      </c>
-      <c r="L27" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27">
+      <c r="L27" s="1">
+        <v>106.38028</v>
+      </c>
+      <c r="M27" t="s">
+        <v>100</v>
+      </c>
+      <c r="N27">
         <v>26939</v>
       </c>
-      <c r="N27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46227</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F28">
-        <v>74.45999999999999</v>
+        <v>74.459</v>
       </c>
       <c r="G28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H28">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I28" s="1">
-        <v>122.86</v>
+        <v>1.649</v>
       </c>
       <c r="J28">
+        <v>122.782891</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.72</v>
       </c>
-      <c r="K28" s="1">
-        <v>128.07</v>
-      </c>
-      <c r="L28" t="s">
-        <v>100</v>
-      </c>
-      <c r="M28">
+      <c r="L28" s="1">
+        <v>128.06948</v>
+      </c>
+      <c r="M28" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28">
         <v>244142</v>
       </c>
-      <c r="N28" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F29">
-        <v>27.92</v>
+        <v>27.922</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H29">
-        <v>1.44</v>
+        <v>1.401</v>
       </c>
       <c r="I29" s="1">
-        <v>40.2</v>
+        <v>1.441</v>
       </c>
       <c r="J29">
+        <v>40.235602</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.54</v>
       </c>
-      <c r="K29" s="1">
-        <v>43</v>
-      </c>
-      <c r="L29" t="s">
-        <v>101</v>
-      </c>
-      <c r="M29">
+      <c r="L29" s="1">
+        <v>42.99988</v>
+      </c>
+      <c r="M29" t="s">
+        <v>102</v>
+      </c>
+      <c r="N29">
         <v>0</v>
       </c>
-      <c r="N29" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46227</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F30">
         <v>339.61</v>
       </c>
       <c r="G30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H30">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I30" s="1">
-        <v>560.36</v>
+        <v>1.649</v>
       </c>
       <c r="J30">
+        <v>560.01689</v>
+      </c>
+      <c r="K30" s="1">
         <v>1.72</v>
       </c>
-      <c r="K30" s="1">
-        <v>584.13</v>
-      </c>
-      <c r="L30" t="s">
-        <v>102</v>
-      </c>
-      <c r="M30">
+      <c r="L30" s="1">
+        <v>584.1292</v>
+      </c>
+      <c r="M30" t="s">
+        <v>103</v>
+      </c>
+      <c r="N30">
         <v>843141</v>
       </c>
-      <c r="N30" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46228</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F31">
         <v>48.54</v>
       </c>
       <c r="G31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H31">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I31" s="1">
-        <v>80.09</v>
+        <v>1.649</v>
       </c>
       <c r="J31">
+        <v>80.04246000000001</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.74</v>
       </c>
-      <c r="K31" s="1">
-        <v>84.45999999999999</v>
-      </c>
-      <c r="L31" t="s">
-        <v>103</v>
-      </c>
-      <c r="M31">
+      <c r="L31" s="1">
+        <v>84.45959999999999</v>
+      </c>
+      <c r="M31" t="s">
+        <v>104</v>
+      </c>
+      <c r="N31">
         <v>190763</v>
       </c>
-      <c r="N31" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46230</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F32">
-        <v>57.7</v>
+        <v>57.701</v>
       </c>
       <c r="G32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H32">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I32" s="1">
-        <v>95.2</v>
+        <v>1.649</v>
       </c>
       <c r="J32">
+        <v>95.148949</v>
+      </c>
+      <c r="K32" s="1">
         <v>1.74</v>
       </c>
-      <c r="K32" s="1">
-        <v>100.4</v>
-      </c>
-      <c r="L32" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32">
+      <c r="L32" s="1">
+        <v>100.39974</v>
+      </c>
+      <c r="M32" t="s">
+        <v>105</v>
+      </c>
+      <c r="N32">
         <v>225083</v>
       </c>
-      <c r="N32" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F33">
-        <v>53.41</v>
+        <v>53.414</v>
       </c>
       <c r="G33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H33">
-        <v>1.68</v>
+        <v>1.653</v>
       </c>
       <c r="I33" s="1">
-        <v>89.73</v>
+        <v>1.683</v>
       </c>
       <c r="J33">
+        <v>89.895762</v>
+      </c>
+      <c r="K33" s="1">
         <v>1.74</v>
       </c>
-      <c r="K33" s="1">
-        <v>92.93000000000001</v>
-      </c>
-      <c r="L33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M33">
+      <c r="L33" s="1">
+        <v>92.94036</v>
+      </c>
+      <c r="M33" t="s">
+        <v>106</v>
+      </c>
+      <c r="N33">
         <v>324658</v>
       </c>
-      <c r="N33" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46232</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F34">
-        <v>73.48999999999999</v>
+        <v>73.492</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H34">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I34" s="1">
-        <v>124.93</v>
+        <v>1.704</v>
       </c>
       <c r="J34">
+        <v>125.230368</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.77</v>
       </c>
-      <c r="K34" s="1">
-        <v>130.08</v>
-      </c>
-      <c r="L34" t="s">
-        <v>106</v>
-      </c>
-      <c r="M34">
+      <c r="L34" s="1">
+        <v>130.08084</v>
+      </c>
+      <c r="M34" t="s">
+        <v>107</v>
+      </c>
+      <c r="N34">
         <v>225836</v>
       </c>
-      <c r="N34" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46232</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35">
-        <v>84.41</v>
+        <v>84.411</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H35">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I35" s="1">
-        <v>143.5</v>
+        <v>1.704</v>
       </c>
       <c r="J35">
+        <v>143.836344</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.75</v>
       </c>
-      <c r="K35" s="1">
-        <v>147.72</v>
-      </c>
-      <c r="L35" t="s">
-        <v>107</v>
-      </c>
-      <c r="M35">
+      <c r="L35" s="1">
+        <v>147.71925</v>
+      </c>
+      <c r="M35" t="s">
+        <v>108</v>
+      </c>
+      <c r="N35">
         <v>251680</v>
       </c>
-      <c r="N35" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F36">
-        <v>83.09</v>
+        <v>83.092</v>
       </c>
       <c r="G36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H36">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I36" s="1">
-        <v>141.25</v>
+        <v>1.704</v>
       </c>
       <c r="J36">
+        <v>141.588768</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.74</v>
       </c>
-      <c r="K36" s="1">
-        <v>144.58</v>
-      </c>
-      <c r="L36" t="s">
-        <v>108</v>
-      </c>
-      <c r="M36">
+      <c r="L36" s="1">
+        <v>144.58008</v>
+      </c>
+      <c r="M36" t="s">
+        <v>109</v>
+      </c>
+      <c r="N36">
         <v>209134</v>
       </c>
-      <c r="N36" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46232</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F37">
-        <v>341.81</v>
+        <v>341.811</v>
       </c>
       <c r="G37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H37">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I37" s="1">
-        <v>581.08</v>
+        <v>1.704</v>
       </c>
       <c r="J37">
+        <v>582.4459440000001</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.75</v>
       </c>
-      <c r="K37" s="1">
-        <v>598.17</v>
-      </c>
-      <c r="L37" t="s">
-        <v>109</v>
-      </c>
-      <c r="M37">
+      <c r="L37" s="1">
+        <v>598.16925</v>
+      </c>
+      <c r="M37" t="s">
+        <v>110</v>
+      </c>
+      <c r="N37">
         <v>0</v>
       </c>
-      <c r="N37" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46232</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F38">
         <v>70.64</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H38">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I38" s="1">
-        <v>120.09</v>
+        <v>1.704</v>
       </c>
       <c r="J38">
+        <v>120.37056</v>
+      </c>
+      <c r="K38" s="1">
         <v>1.75</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>123.62</v>
       </c>
-      <c r="L38" t="s">
-        <v>110</v>
-      </c>
-      <c r="M38">
+      <c r="M38" t="s">
+        <v>111</v>
+      </c>
+      <c r="N38">
         <v>82270</v>
       </c>
-      <c r="N38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46233</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F39">
-        <v>50.55</v>
+        <v>50.548</v>
       </c>
       <c r="G39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H39">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I39" s="1">
-        <v>75.31999999999999</v>
+        <v>1.489</v>
       </c>
       <c r="J39">
+        <v>75.265972</v>
+      </c>
+      <c r="K39" s="1">
         <v>1.55</v>
       </c>
-      <c r="K39" s="1">
-        <v>78.34999999999999</v>
-      </c>
-      <c r="L39" t="s">
-        <v>111</v>
-      </c>
-      <c r="M39">
+      <c r="L39" s="1">
+        <v>78.3494</v>
+      </c>
+      <c r="M39" t="s">
+        <v>112</v>
+      </c>
+      <c r="N39">
         <v>0</v>
       </c>
-      <c r="N39" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46233</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F40">
-        <v>74.02</v>
+        <v>74.023</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H40">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I40" s="1">
-        <v>125.83</v>
+        <v>1.704</v>
       </c>
       <c r="J40">
+        <v>126.135192</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.76</v>
       </c>
-      <c r="K40" s="1">
-        <v>130.28</v>
-      </c>
-      <c r="L40" t="s">
-        <v>112</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>130.28048</v>
+      </c>
+      <c r="M40" t="s">
+        <v>113</v>
+      </c>
+      <c r="N40">
         <v>62623</v>
       </c>
-      <c r="N40" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46233</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F41">
-        <v>72.98</v>
+        <v>72.977</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H41">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I41" s="1">
-        <v>124.07</v>
+        <v>1.704</v>
       </c>
       <c r="J41">
+        <v>124.352808</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.76</v>
       </c>
-      <c r="K41" s="1">
-        <v>128.44</v>
-      </c>
-      <c r="L41" t="s">
-        <v>113</v>
-      </c>
-      <c r="M41">
+      <c r="L41" s="1">
+        <v>128.43952</v>
+      </c>
+      <c r="M41" t="s">
+        <v>114</v>
+      </c>
+      <c r="N41">
         <v>191270</v>
       </c>
-      <c r="N41" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F42">
-        <v>67.86</v>
+        <v>67.858</v>
       </c>
       <c r="G42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H42">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I42" s="1">
-        <v>115.36</v>
+        <v>1.704</v>
       </c>
       <c r="J42">
+        <v>115.630032</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.76</v>
       </c>
-      <c r="K42" s="1">
-        <v>119.43</v>
-      </c>
-      <c r="L42" t="s">
-        <v>114</v>
-      </c>
-      <c r="M42">
+      <c r="L42" s="1">
+        <v>119.43008</v>
+      </c>
+      <c r="M42" t="s">
+        <v>115</v>
+      </c>
+      <c r="N42">
         <v>325266</v>
       </c>
-      <c r="N42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46233</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43">
-        <v>44.15</v>
+        <v>44.148</v>
       </c>
       <c r="G43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H43">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I43" s="1">
-        <v>75.05</v>
+        <v>1.704</v>
       </c>
       <c r="J43">
+        <v>75.22819200000001</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.76</v>
       </c>
-      <c r="K43" s="1">
-        <v>77.7</v>
-      </c>
-      <c r="L43" t="s">
-        <v>115</v>
-      </c>
-      <c r="M43">
+      <c r="L43" s="1">
+        <v>77.70048</v>
+      </c>
+      <c r="M43" t="s">
+        <v>116</v>
+      </c>
+      <c r="N43">
         <v>0</v>
       </c>
-      <c r="N43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46233</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F44">
-        <v>67.44</v>
+        <v>67.438</v>
       </c>
       <c r="G44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H44">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I44" s="1">
-        <v>114.65</v>
+        <v>1.704</v>
       </c>
       <c r="J44">
+        <v>114.914352</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.76</v>
       </c>
-      <c r="K44" s="1">
-        <v>118.69</v>
-      </c>
-      <c r="L44" t="s">
-        <v>116</v>
-      </c>
-      <c r="M44">
+      <c r="L44" s="1">
+        <v>118.69088</v>
+      </c>
+      <c r="M44" t="s">
+        <v>117</v>
+      </c>
+      <c r="N44">
         <v>209696</v>
       </c>
-      <c r="N44" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3">
         <v>46233</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F45">
-        <v>75.97</v>
+        <v>75.97199999999999</v>
       </c>
       <c r="G45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H45">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I45" s="1">
-        <v>129.15</v>
+        <v>1.704</v>
       </c>
       <c r="J45">
+        <v>129.456288</v>
+      </c>
+      <c r="K45" s="1">
         <v>1.79</v>
       </c>
-      <c r="K45" s="1">
-        <v>135.99</v>
-      </c>
-      <c r="L45" t="s">
-        <v>117</v>
-      </c>
-      <c r="M45">
+      <c r="L45" s="1">
+        <v>135.98988</v>
+      </c>
+      <c r="M45" t="s">
+        <v>118</v>
+      </c>
+      <c r="N45">
         <v>226536</v>
       </c>
-      <c r="N45" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3">
         <v>46233</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F46">
-        <v>31.36</v>
+        <v>31.361</v>
       </c>
       <c r="G46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H46">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I46" s="1">
-        <v>46.73</v>
+        <v>1.489</v>
       </c>
       <c r="J46">
+        <v>46.696529</v>
+      </c>
+      <c r="K46" s="1">
         <v>1.55</v>
       </c>
-      <c r="K46" s="1">
-        <v>48.61</v>
-      </c>
-      <c r="L46" t="s">
-        <v>118</v>
-      </c>
-      <c r="M46">
+      <c r="L46" s="1">
+        <v>48.60955</v>
+      </c>
+      <c r="M46" t="s">
+        <v>119</v>
+      </c>
+      <c r="N46">
         <v>132219</v>
       </c>
-      <c r="N46" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F47">
-        <v>22.59</v>
+        <v>22.587</v>
       </c>
       <c r="G47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H47">
-        <v>1.5</v>
+        <v>1.459</v>
       </c>
       <c r="I47" s="1">
-        <v>33.88</v>
+        <v>1.499</v>
       </c>
       <c r="J47">
+        <v>33.857913</v>
+      </c>
+      <c r="K47" s="1">
         <v>1.55</v>
       </c>
-      <c r="K47" s="1">
-        <v>35.01</v>
-      </c>
-      <c r="L47" t="s">
-        <v>119</v>
-      </c>
-      <c r="M47">
+      <c r="L47" s="1">
+        <v>35.00985</v>
+      </c>
+      <c r="M47" t="s">
+        <v>120</v>
+      </c>
+      <c r="N47">
         <v>229742</v>
       </c>
-      <c r="N47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F48">
-        <v>16.42</v>
+        <v>16.422</v>
       </c>
       <c r="G48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H48">
         <v>0.64</v>
       </c>
       <c r="I48" s="1">
-        <v>10.51</v>
+        <v>0.64</v>
       </c>
       <c r="J48">
+        <v>10.51008</v>
+      </c>
+      <c r="K48" s="1">
         <v>0.64</v>
       </c>
-      <c r="K48" s="1">
-        <v>10.51</v>
-      </c>
-      <c r="L48" t="s">
-        <v>119</v>
-      </c>
-      <c r="M48">
+      <c r="L48" s="1">
+        <v>10.51008</v>
+      </c>
+      <c r="M48" t="s">
+        <v>120</v>
+      </c>
+      <c r="N48">
         <v>229742</v>
       </c>
-      <c r="N48" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="3">
         <v>46234</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F49">
-        <v>23.59</v>
+        <v>23.588</v>
       </c>
       <c r="G49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H49">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I49" s="1">
-        <v>40.57</v>
+        <v>1.719</v>
       </c>
       <c r="J49">
+        <v>40.547772</v>
+      </c>
+      <c r="K49" s="1">
         <v>1.77</v>
       </c>
-      <c r="K49" s="1">
-        <v>41.75</v>
-      </c>
-      <c r="L49" t="s">
-        <v>120</v>
-      </c>
-      <c r="M49">
+      <c r="L49" s="1">
+        <v>41.75076</v>
+      </c>
+      <c r="M49" t="s">
+        <v>121</v>
+      </c>
+      <c r="N49">
         <v>209896</v>
       </c>
-      <c r="N49" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="3">
         <v>46234</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F50">
-        <v>76.93000000000001</v>
+        <v>76.932</v>
       </c>
       <c r="G50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H50">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I50" s="1">
-        <v>132.32</v>
+        <v>1.719</v>
       </c>
       <c r="J50">
+        <v>132.246108</v>
+      </c>
+      <c r="K50" s="1">
         <v>1.77</v>
       </c>
-      <c r="K50" s="1">
-        <v>136.17</v>
-      </c>
-      <c r="L50" t="s">
-        <v>121</v>
-      </c>
-      <c r="M50">
+      <c r="L50" s="1">
+        <v>136.16964</v>
+      </c>
+      <c r="M50" t="s">
+        <v>122</v>
+      </c>
+      <c r="N50">
         <v>252260</v>
       </c>
-      <c r="N50" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="3">
         <v>46234</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F51">
-        <v>55.75</v>
+        <v>55.748</v>
       </c>
       <c r="G51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H51">
-        <v>1.5</v>
+        <v>1.459</v>
       </c>
       <c r="I51" s="1">
-        <v>83.62</v>
+        <v>1.499</v>
       </c>
       <c r="J51">
+        <v>83.56625200000001</v>
+      </c>
+      <c r="K51" s="1">
         <v>1.55</v>
       </c>
-      <c r="K51" s="1">
-        <v>86.41</v>
-      </c>
-      <c r="L51" t="s">
-        <v>122</v>
-      </c>
-      <c r="M51">
+      <c r="L51" s="1">
+        <v>86.40940000000001</v>
+      </c>
+      <c r="M51" t="s">
+        <v>123</v>
+      </c>
+      <c r="N51">
         <v>0</v>
       </c>
-      <c r="N51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3">
         <v>46234</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F52">
-        <v>12.63</v>
+        <v>12.632</v>
       </c>
       <c r="G52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H52">
-        <v>1.5</v>
+        <v>1.459</v>
       </c>
       <c r="I52" s="1">
-        <v>18.94</v>
+        <v>1.499</v>
       </c>
       <c r="J52">
+        <v>18.935368</v>
+      </c>
+      <c r="K52" s="1">
         <v>1.55</v>
       </c>
-      <c r="K52" s="1">
-        <v>19.58</v>
-      </c>
-      <c r="L52" t="s">
-        <v>123</v>
-      </c>
-      <c r="M52">
+      <c r="L52" s="1">
+        <v>19.5796</v>
+      </c>
+      <c r="M52" t="s">
+        <v>124</v>
+      </c>
+      <c r="N52">
         <v>132367</v>
       </c>
-      <c r="N52" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F53">
-        <v>46.88</v>
+        <v>46.881</v>
       </c>
       <c r="G53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H53">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I53" s="1">
-        <v>80.63</v>
+        <v>1.719</v>
       </c>
       <c r="J53">
+        <v>80.58843899999999</v>
+      </c>
+      <c r="K53" s="1">
         <v>1.77</v>
       </c>
-      <c r="K53" s="1">
-        <v>82.98</v>
-      </c>
-      <c r="L53" t="s">
-        <v>120</v>
-      </c>
-      <c r="M53">
+      <c r="L53" s="1">
+        <v>82.97937</v>
+      </c>
+      <c r="M53" t="s">
+        <v>121</v>
+      </c>
+      <c r="N53">
         <v>325631</v>
       </c>
-      <c r="N53" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F54">
-        <v>38.33</v>
+        <v>38.331</v>
       </c>
       <c r="G54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H54">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I54" s="1">
-        <v>65.93000000000001</v>
+        <v>1.719</v>
       </c>
       <c r="J54">
+        <v>65.890989</v>
+      </c>
+      <c r="K54" s="1">
         <v>1.78</v>
       </c>
-      <c r="K54" s="1">
-        <v>68.23</v>
-      </c>
-      <c r="L54" t="s">
-        <v>124</v>
-      </c>
-      <c r="M54">
+      <c r="L54" s="1">
+        <v>68.22918</v>
+      </c>
+      <c r="M54" t="s">
+        <v>125</v>
+      </c>
+      <c r="N54">
         <v>226919</v>
       </c>
-      <c r="N54" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="3">
         <v>46234</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F55">
-        <v>54.32</v>
+        <v>54.322</v>
       </c>
       <c r="G55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H55">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I55" s="1">
-        <v>93.43000000000001</v>
+        <v>1.719</v>
       </c>
       <c r="J55">
+        <v>93.379518</v>
+      </c>
+      <c r="K55" s="1">
         <v>1.77</v>
       </c>
-      <c r="K55" s="1">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="L55" t="s">
-        <v>125</v>
-      </c>
-      <c r="M55">
+      <c r="L55" s="1">
+        <v>96.14994</v>
+      </c>
+      <c r="M55" t="s">
+        <v>126</v>
+      </c>
+      <c r="N55">
         <v>244564</v>
       </c>
-      <c r="N55" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="3">
         <v>46234</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E56" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F56">
         <v>0.61</v>
       </c>
       <c r="G56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H56">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I56" s="1">
-        <v>1.05</v>
+        <v>1.719</v>
       </c>
       <c r="J56">
+        <v>1.04859</v>
+      </c>
+      <c r="K56" s="1">
         <v>1.77</v>
       </c>
-      <c r="K56" s="1">
-        <v>1.08</v>
-      </c>
-      <c r="L56" t="s">
-        <v>126</v>
-      </c>
-      <c r="M56">
+      <c r="L56" s="1">
+        <v>1.0797</v>
+      </c>
+      <c r="M56" t="s">
+        <v>127</v>
+      </c>
+      <c r="N56">
         <v>0</v>
       </c>
-      <c r="N56" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="3">
         <v>46234</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F57">
-        <v>73.5</v>
+        <v>73.503</v>
       </c>
       <c r="G57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H57">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I57" s="1">
-        <v>126.42</v>
+        <v>1.719</v>
       </c>
       <c r="J57">
+        <v>126.351657</v>
+      </c>
+      <c r="K57" s="1">
         <v>1.77</v>
       </c>
-      <c r="K57" s="1">
-        <v>130.1</v>
-      </c>
-      <c r="L57" t="s">
-        <v>127</v>
-      </c>
-      <c r="M57">
+      <c r="L57" s="1">
+        <v>130.10031</v>
+      </c>
+      <c r="M57" t="s">
+        <v>128</v>
+      </c>
+      <c r="N57">
         <v>27664</v>
       </c>
-      <c r="N57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="3">
         <v>46234</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F58">
         <v>27.59</v>
       </c>
       <c r="G58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H58">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I58" s="1">
-        <v>47.45</v>
+        <v>1.719</v>
       </c>
       <c r="J58">
+        <v>47.42721</v>
+      </c>
+      <c r="K58" s="1">
         <v>1.78</v>
       </c>
-      <c r="K58" s="1">
-        <v>49.11</v>
-      </c>
-      <c r="L58" t="s">
-        <v>128</v>
-      </c>
-      <c r="M58">
+      <c r="L58" s="1">
+        <v>49.1102</v>
+      </c>
+      <c r="M58" t="s">
+        <v>129</v>
+      </c>
+      <c r="N58">
         <v>0</v>
       </c>
-      <c r="N58" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O58" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3569,61 +3746,61 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:15">
       <c r="A62" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="7">
-        <v>4469.89</v>
+        <v>4469.9</v>
       </c>
       <c r="C63" s="7">
         <v>46</v>
       </c>
       <c r="D63" s="8">
-        <v>1.628897</v>
+        <v>1.629611</v>
       </c>
       <c r="E63" s="7">
-        <v>7280.99</v>
+        <v>7284.2</v>
       </c>
       <c r="F63" s="7">
-        <v>7604.78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+        <v>7604.81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B64" s="7">
-        <v>319.9</v>
+        <v>319.893</v>
       </c>
       <c r="C64" s="7">
         <v>9</v>
       </c>
       <c r="D64" s="8">
-        <v>1.468928</v>
+        <v>1.468745</v>
       </c>
       <c r="E64" s="7">
-        <v>469.91</v>
+        <v>469.84</v>
       </c>
       <c r="F64" s="7">
         <v>494.09</v>
@@ -3631,7 +3808,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="7">
         <v>61.99</v>
@@ -3640,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="8">
-        <v>1.909985</v>
+        <v>1.91</v>
       </c>
       <c r="E65" s="7">
         <v>118.4</v>
@@ -3651,16 +3828,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" s="7">
-        <v>16.42</v>
+        <v>16.422</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" s="8">
-        <v>0.640073</v>
+        <v>0.64</v>
       </c>
       <c r="E66" s="7">
         <v>10.51</v>
@@ -3671,20 +3848,20 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="10">
-        <v>4868.2</v>
+        <v>4868.205</v>
       </c>
       <c r="C67" s="10">
         <v>57</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="10">
-        <v>7879.81</v>
+        <v>7882.95</v>
       </c>
       <c r="F67" s="10">
-        <v>8227.780000000001</v>
+        <v>8227.809999999999</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ФУУДС ТРЕЙД ЕООД/ФУУДС ТРЕЙД ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="191">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -597,9 +594,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -693,10 +690,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -991,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1004,13 +1001,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1053,2692 +1050,2518 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2">
         <v>318.019</v>
       </c>
       <c r="G2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2">
+        <v>1.529</v>
+      </c>
+      <c r="I2" s="1">
+        <v>486.251</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>512.011</v>
+      </c>
+      <c r="L2" t="s">
         <v>74</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.529</v>
-      </c>
-      <c r="J2">
-        <v>486.251051</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>512.01059</v>
-      </c>
-      <c r="M2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>841060</v>
       </c>
-      <c r="O2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>321.731</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I3" s="1">
-        <v>1.529</v>
+        <v>491.927</v>
       </c>
       <c r="J3">
-        <v>491.926699</v>
+        <v>1.6</v>
       </c>
       <c r="K3" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="L3" s="1">
-        <v>514.7696</v>
-      </c>
-      <c r="M3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N3">
+        <v>514.77</v>
+      </c>
+      <c r="L3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>81.199</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I4" s="1">
-        <v>1.529</v>
+        <v>124.153</v>
       </c>
       <c r="J4">
-        <v>124.153271</v>
+        <v>1.61</v>
       </c>
       <c r="K4" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L4" s="1">
-        <v>130.73039</v>
-      </c>
-      <c r="M4" t="s">
-        <v>77</v>
-      </c>
-      <c r="N4">
+        <v>130.73</v>
+      </c>
+      <c r="L4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4">
         <v>249703</v>
       </c>
-      <c r="O4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>49.783</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I5" s="1">
-        <v>1.529</v>
+        <v>76.11799999999999</v>
       </c>
       <c r="J5">
-        <v>76.118207</v>
+        <v>1.61</v>
       </c>
       <c r="K5" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L5" s="1">
-        <v>80.15063000000001</v>
-      </c>
-      <c r="M5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5">
+        <v>80.151</v>
+      </c>
+      <c r="L5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5">
         <v>422109</v>
       </c>
-      <c r="O5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>67.712</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I6" s="1">
-        <v>1.529</v>
+        <v>103.532</v>
       </c>
       <c r="J6">
-        <v>103.531648</v>
+        <v>1.63</v>
       </c>
       <c r="K6" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L6" s="1">
-        <v>110.37056</v>
-      </c>
-      <c r="M6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6">
+        <v>110.371</v>
+      </c>
+      <c r="L6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6">
         <v>323048</v>
       </c>
-      <c r="O6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>55.509</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I7" s="1">
-        <v>1.529</v>
+        <v>84.873</v>
       </c>
       <c r="J7">
-        <v>84.873261</v>
+        <v>1.63</v>
       </c>
       <c r="K7" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L7" s="1">
-        <v>90.47967</v>
-      </c>
-      <c r="M7" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7">
+        <v>90.48</v>
+      </c>
+      <c r="L7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7">
         <v>223627</v>
       </c>
-      <c r="O7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46221</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>57.57</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H8">
-        <v>1.528</v>
+        <v>1.558</v>
       </c>
       <c r="I8" s="1">
-        <v>1.558</v>
+        <v>89.694</v>
       </c>
       <c r="J8">
-        <v>89.69405999999999</v>
+        <v>1.65</v>
       </c>
       <c r="K8" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L8" s="1">
-        <v>94.9905</v>
-      </c>
-      <c r="M8" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46221</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9">
         <v>61.99</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H9">
         <v>1.91</v>
       </c>
       <c r="I9" s="1">
+        <v>118.401</v>
+      </c>
+      <c r="J9">
         <v>1.91</v>
       </c>
-      <c r="J9">
-        <v>118.4009</v>
-      </c>
       <c r="K9" s="1">
-        <v>1.91</v>
-      </c>
-      <c r="L9" s="1">
-        <v>118.4009</v>
-      </c>
-      <c r="M9" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9">
+        <v>118.401</v>
+      </c>
+      <c r="L9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F10">
         <v>27.699</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H10">
-        <v>1.389</v>
+        <v>1.429</v>
       </c>
       <c r="I10" s="1">
-        <v>1.429</v>
+        <v>39.582</v>
       </c>
       <c r="J10">
-        <v>39.581871</v>
+        <v>1.53</v>
       </c>
       <c r="K10" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L10" s="1">
-        <v>42.37947</v>
-      </c>
-      <c r="M10" t="s">
-        <v>83</v>
-      </c>
-      <c r="N10">
+        <v>42.379</v>
+      </c>
+      <c r="L10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46224</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11">
         <v>350.509</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H11">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I11" s="1">
-        <v>1.594</v>
+        <v>558.711</v>
       </c>
       <c r="J11">
-        <v>558.711346</v>
+        <v>1.69</v>
       </c>
       <c r="K11" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L11" s="1">
-        <v>592.3602100000001</v>
-      </c>
-      <c r="M11" t="s">
-        <v>84</v>
-      </c>
-      <c r="N11">
+        <v>592.36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46224</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>70.488</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H12">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I12" s="1">
-        <v>1.594</v>
+        <v>112.358</v>
       </c>
       <c r="J12">
-        <v>112.357872</v>
+        <v>1.66</v>
       </c>
       <c r="K12" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="L12" s="1">
-        <v>117.01008</v>
-      </c>
-      <c r="M12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N12">
+        <v>117.01</v>
+      </c>
+      <c r="L12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12">
         <v>323603</v>
       </c>
-      <c r="O12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46224</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13">
         <v>50.714</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H13">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I13" s="1">
-        <v>1.594</v>
+        <v>80.83799999999999</v>
       </c>
       <c r="J13">
-        <v>80.838116</v>
+        <v>1.68</v>
       </c>
       <c r="K13" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L13" s="1">
-        <v>85.19952000000001</v>
-      </c>
-      <c r="M13" t="s">
-        <v>86</v>
-      </c>
-      <c r="N13">
+        <v>85.2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>85</v>
+      </c>
+      <c r="M13">
         <v>224123</v>
       </c>
-      <c r="O13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46224</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <v>76.03</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I14" s="1">
-        <v>1.594</v>
+        <v>121.192</v>
       </c>
       <c r="J14">
-        <v>121.19182</v>
+        <v>1.68</v>
       </c>
       <c r="K14" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L14" s="1">
-        <v>127.7304</v>
-      </c>
-      <c r="M14" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14">
+        <v>127.73</v>
+      </c>
+      <c r="L14" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14">
         <v>81677</v>
       </c>
-      <c r="O14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46224</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15">
         <v>56.071</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H15">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I15" s="1">
-        <v>1.594</v>
+        <v>89.377</v>
       </c>
       <c r="J15">
-        <v>89.377174</v>
+        <v>1.68</v>
       </c>
       <c r="K15" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L15" s="1">
-        <v>94.19928</v>
-      </c>
-      <c r="M15" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15">
+        <v>94.199</v>
+      </c>
+      <c r="L15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46225</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16">
         <v>53.799</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H16">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I16" s="1">
-        <v>1.441</v>
+        <v>77.524</v>
       </c>
       <c r="J16">
-        <v>77.524359</v>
+        <v>1.54</v>
       </c>
       <c r="K16" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L16" s="1">
-        <v>82.85046</v>
-      </c>
-      <c r="M16" t="s">
-        <v>89</v>
-      </c>
-      <c r="N16">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
-      <c r="O16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46225</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17">
         <v>87.627</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H17">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I17" s="1">
-        <v>1.618</v>
+        <v>141.78</v>
       </c>
       <c r="J17">
-        <v>141.780486</v>
+        <v>1.69</v>
       </c>
       <c r="K17" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L17" s="1">
-        <v>148.08963</v>
-      </c>
-      <c r="M17" t="s">
-        <v>90</v>
-      </c>
-      <c r="N17">
+        <v>148.09</v>
+      </c>
+      <c r="L17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17">
         <v>208372</v>
       </c>
-      <c r="O17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46225</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18">
         <v>320.588</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H18">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I18" s="1">
-        <v>1.618</v>
+        <v>518.711</v>
       </c>
       <c r="J18">
-        <v>518.711384</v>
+        <v>1.7</v>
       </c>
       <c r="K18" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L18" s="1">
-        <v>544.9996</v>
-      </c>
-      <c r="M18" t="s">
-        <v>91</v>
-      </c>
-      <c r="N18">
+        <v>545</v>
+      </c>
+      <c r="L18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18">
         <v>842085</v>
       </c>
-      <c r="O18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19">
         <v>51.448</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H19">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I19" s="1">
-        <v>1.618</v>
+        <v>83.24299999999999</v>
       </c>
       <c r="J19">
-        <v>83.242864</v>
+        <v>1.72</v>
       </c>
       <c r="K19" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L19" s="1">
-        <v>88.49056</v>
-      </c>
-      <c r="M19" t="s">
-        <v>92</v>
-      </c>
-      <c r="N19">
+        <v>88.491</v>
+      </c>
+      <c r="L19" t="s">
+        <v>91</v>
+      </c>
+      <c r="M19">
         <v>224607</v>
       </c>
-      <c r="O19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F20">
         <v>74.911</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H20">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I20" s="1">
-        <v>1.618</v>
+        <v>121.206</v>
       </c>
       <c r="J20">
-        <v>121.205998</v>
+        <v>1.69</v>
       </c>
       <c r="K20" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L20" s="1">
-        <v>126.59959</v>
-      </c>
-      <c r="M20" t="s">
-        <v>93</v>
-      </c>
-      <c r="N20">
+        <v>126.6</v>
+      </c>
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20">
         <v>250330</v>
       </c>
-      <c r="O20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21">
         <v>75.441</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H21">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I21" s="1">
-        <v>1.618</v>
+        <v>122.064</v>
       </c>
       <c r="J21">
-        <v>122.063538</v>
+        <v>1.7</v>
       </c>
       <c r="K21" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L21" s="1">
-        <v>128.2497</v>
-      </c>
-      <c r="M21" t="s">
-        <v>94</v>
-      </c>
-      <c r="N21">
+        <v>128.25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21">
         <v>190435</v>
       </c>
-      <c r="O21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22">
         <v>66.56699999999999</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H22">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I22" s="1">
-        <v>1.618</v>
+        <v>107.705</v>
       </c>
       <c r="J22">
-        <v>107.705406</v>
+        <v>1.71</v>
       </c>
       <c r="K22" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L22" s="1">
-        <v>113.82957</v>
-      </c>
-      <c r="M22" t="s">
-        <v>95</v>
-      </c>
-      <c r="N22">
+        <v>113.83</v>
+      </c>
+      <c r="L22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22">
         <v>680680</v>
       </c>
-      <c r="O22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46226</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23">
         <v>68.274</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H23">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I23" s="1">
-        <v>1.618</v>
+        <v>110.467</v>
       </c>
       <c r="J23">
-        <v>110.467332</v>
+        <v>1.68</v>
       </c>
       <c r="K23" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L23" s="1">
-        <v>114.70032</v>
-      </c>
-      <c r="M23" t="s">
-        <v>96</v>
-      </c>
-      <c r="N23">
+        <v>114.7</v>
+      </c>
+      <c r="L23" t="s">
+        <v>95</v>
+      </c>
+      <c r="M23">
         <v>324195</v>
       </c>
-      <c r="O23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46226</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24">
         <v>53.639</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I24" s="1">
-        <v>1.618</v>
+        <v>86.788</v>
       </c>
       <c r="J24">
-        <v>86.787902</v>
+        <v>1.69</v>
       </c>
       <c r="K24" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L24" s="1">
-        <v>90.64991000000001</v>
-      </c>
-      <c r="M24" t="s">
-        <v>97</v>
-      </c>
-      <c r="N24">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="L24" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F25">
         <v>37.597</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H25">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I25" s="1">
-        <v>1.441</v>
+        <v>54.177</v>
       </c>
       <c r="J25">
-        <v>54.177277</v>
+        <v>1.54</v>
       </c>
       <c r="K25" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L25" s="1">
-        <v>57.89938</v>
-      </c>
-      <c r="M25" t="s">
-        <v>98</v>
-      </c>
-      <c r="N25">
+        <v>57.899</v>
+      </c>
+      <c r="L25" t="s">
+        <v>97</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46227</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26">
         <v>82.878</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H26">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I26" s="1">
-        <v>1.649</v>
+        <v>136.666</v>
       </c>
       <c r="J26">
-        <v>136.665822</v>
+        <v>1.72</v>
       </c>
       <c r="K26" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L26" s="1">
-        <v>142.55016</v>
-      </c>
-      <c r="M26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N26">
+        <v>142.55</v>
+      </c>
+      <c r="L26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M26">
         <v>251005</v>
       </c>
-      <c r="O26" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46227</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27">
         <v>61.849</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I27" s="1">
-        <v>1.649</v>
+        <v>101.989</v>
       </c>
       <c r="J27">
-        <v>101.989001</v>
+        <v>1.72</v>
       </c>
       <c r="K27" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L27" s="1">
-        <v>106.38028</v>
-      </c>
-      <c r="M27" t="s">
-        <v>100</v>
-      </c>
-      <c r="N27">
+        <v>106.38</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27">
         <v>26939</v>
       </c>
-      <c r="O27" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46227</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28">
         <v>74.459</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H28">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I28" s="1">
-        <v>1.649</v>
+        <v>122.783</v>
       </c>
       <c r="J28">
-        <v>122.782891</v>
+        <v>1.72</v>
       </c>
       <c r="K28" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L28" s="1">
-        <v>128.06948</v>
-      </c>
-      <c r="M28" t="s">
-        <v>101</v>
-      </c>
-      <c r="N28">
+        <v>128.069</v>
+      </c>
+      <c r="L28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28">
         <v>244142</v>
       </c>
-      <c r="O28" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29">
         <v>27.922</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I29" s="1">
-        <v>1.441</v>
+        <v>40.236</v>
       </c>
       <c r="J29">
-        <v>40.235602</v>
+        <v>1.54</v>
       </c>
       <c r="K29" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L29" s="1">
-        <v>42.99988</v>
-      </c>
-      <c r="M29" t="s">
-        <v>102</v>
-      </c>
-      <c r="N29">
+        <v>43</v>
+      </c>
+      <c r="L29" t="s">
+        <v>101</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
-      <c r="O29" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46227</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F30">
         <v>339.61</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H30">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I30" s="1">
-        <v>1.649</v>
+        <v>560.0170000000001</v>
       </c>
       <c r="J30">
-        <v>560.01689</v>
+        <v>1.72</v>
       </c>
       <c r="K30" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L30" s="1">
-        <v>584.1292</v>
-      </c>
-      <c r="M30" t="s">
-        <v>103</v>
-      </c>
-      <c r="N30">
+        <v>584.129</v>
+      </c>
+      <c r="L30" t="s">
+        <v>102</v>
+      </c>
+      <c r="M30">
         <v>843141</v>
       </c>
-      <c r="O30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46228</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F31">
         <v>48.54</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H31">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I31" s="1">
-        <v>1.649</v>
+        <v>80.042</v>
       </c>
       <c r="J31">
-        <v>80.04246000000001</v>
+        <v>1.74</v>
       </c>
       <c r="K31" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L31" s="1">
-        <v>84.45959999999999</v>
-      </c>
-      <c r="M31" t="s">
-        <v>104</v>
-      </c>
-      <c r="N31">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="L31" t="s">
+        <v>103</v>
+      </c>
+      <c r="M31">
         <v>190763</v>
       </c>
-      <c r="O31" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46230</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32">
         <v>57.701</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H32">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I32" s="1">
-        <v>1.649</v>
+        <v>95.149</v>
       </c>
       <c r="J32">
-        <v>95.148949</v>
+        <v>1.74</v>
       </c>
       <c r="K32" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L32" s="1">
-        <v>100.39974</v>
-      </c>
-      <c r="M32" t="s">
-        <v>105</v>
-      </c>
-      <c r="N32">
+        <v>100.4</v>
+      </c>
+      <c r="L32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32">
         <v>225083</v>
       </c>
-      <c r="O32" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33">
         <v>53.414</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H33">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I33" s="1">
-        <v>1.683</v>
+        <v>89.896</v>
       </c>
       <c r="J33">
-        <v>89.895762</v>
+        <v>1.74</v>
       </c>
       <c r="K33" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L33" s="1">
-        <v>92.94036</v>
-      </c>
-      <c r="M33" t="s">
-        <v>106</v>
-      </c>
-      <c r="N33">
+        <v>92.94</v>
+      </c>
+      <c r="L33" t="s">
+        <v>105</v>
+      </c>
+      <c r="M33">
         <v>324658</v>
       </c>
-      <c r="O33" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46232</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34">
         <v>73.492</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H34">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I34" s="1">
-        <v>1.704</v>
+        <v>125.23</v>
       </c>
       <c r="J34">
-        <v>125.230368</v>
+        <v>1.77</v>
       </c>
       <c r="K34" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L34" s="1">
-        <v>130.08084</v>
-      </c>
-      <c r="M34" t="s">
-        <v>107</v>
-      </c>
-      <c r="N34">
+        <v>130.081</v>
+      </c>
+      <c r="L34" t="s">
+        <v>106</v>
+      </c>
+      <c r="M34">
         <v>225836</v>
       </c>
-      <c r="O34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46232</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35">
         <v>84.411</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H35">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I35" s="1">
-        <v>1.704</v>
+        <v>143.836</v>
       </c>
       <c r="J35">
-        <v>143.836344</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L35" s="1">
-        <v>147.71925</v>
-      </c>
-      <c r="M35" t="s">
-        <v>108</v>
-      </c>
-      <c r="N35">
+        <v>147.719</v>
+      </c>
+      <c r="L35" t="s">
+        <v>107</v>
+      </c>
+      <c r="M35">
         <v>251680</v>
       </c>
-      <c r="O35" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36">
         <v>83.092</v>
       </c>
       <c r="G36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H36">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I36" s="1">
-        <v>1.704</v>
+        <v>141.589</v>
       </c>
       <c r="J36">
-        <v>141.588768</v>
+        <v>1.74</v>
       </c>
       <c r="K36" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L36" s="1">
-        <v>144.58008</v>
-      </c>
-      <c r="M36" t="s">
-        <v>109</v>
-      </c>
-      <c r="N36">
+        <v>144.58</v>
+      </c>
+      <c r="L36" t="s">
+        <v>108</v>
+      </c>
+      <c r="M36">
         <v>209134</v>
       </c>
-      <c r="O36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46232</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37">
         <v>341.811</v>
       </c>
       <c r="G37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H37">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I37" s="1">
-        <v>1.704</v>
+        <v>582.446</v>
       </c>
       <c r="J37">
-        <v>582.4459440000001</v>
+        <v>1.75</v>
       </c>
       <c r="K37" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L37" s="1">
-        <v>598.16925</v>
-      </c>
-      <c r="M37" t="s">
-        <v>110</v>
-      </c>
-      <c r="N37">
+        <v>598.169</v>
+      </c>
+      <c r="L37" t="s">
+        <v>109</v>
+      </c>
+      <c r="M37">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46232</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38">
         <v>70.64</v>
       </c>
       <c r="G38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H38">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I38" s="1">
-        <v>1.704</v>
+        <v>120.371</v>
       </c>
       <c r="J38">
-        <v>120.37056</v>
+        <v>1.75</v>
       </c>
       <c r="K38" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L38" s="1">
         <v>123.62</v>
       </c>
-      <c r="M38" t="s">
-        <v>111</v>
-      </c>
-      <c r="N38">
+      <c r="L38" t="s">
+        <v>110</v>
+      </c>
+      <c r="M38">
         <v>82270</v>
       </c>
-      <c r="O38" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46233</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F39">
         <v>50.548</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H39">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I39" s="1">
-        <v>1.489</v>
+        <v>75.26600000000001</v>
       </c>
       <c r="J39">
-        <v>75.265972</v>
+        <v>1.55</v>
       </c>
       <c r="K39" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L39" s="1">
-        <v>78.3494</v>
-      </c>
-      <c r="M39" t="s">
-        <v>112</v>
-      </c>
-      <c r="N39">
+        <v>78.349</v>
+      </c>
+      <c r="L39" t="s">
+        <v>111</v>
+      </c>
+      <c r="M39">
         <v>0</v>
       </c>
-      <c r="O39" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46233</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40">
         <v>74.023</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H40">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I40" s="1">
-        <v>1.704</v>
+        <v>126.135</v>
       </c>
       <c r="J40">
-        <v>126.135192</v>
+        <v>1.76</v>
       </c>
       <c r="K40" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L40" s="1">
-        <v>130.28048</v>
-      </c>
-      <c r="M40" t="s">
-        <v>113</v>
-      </c>
-      <c r="N40">
+        <v>130.28</v>
+      </c>
+      <c r="L40" t="s">
+        <v>112</v>
+      </c>
+      <c r="M40">
         <v>62623</v>
       </c>
-      <c r="O40" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46233</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41">
         <v>72.977</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H41">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I41" s="1">
-        <v>1.704</v>
+        <v>124.353</v>
       </c>
       <c r="J41">
-        <v>124.352808</v>
+        <v>1.76</v>
       </c>
       <c r="K41" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L41" s="1">
-        <v>128.43952</v>
-      </c>
-      <c r="M41" t="s">
-        <v>114</v>
-      </c>
-      <c r="N41">
+        <v>128.44</v>
+      </c>
+      <c r="L41" t="s">
+        <v>113</v>
+      </c>
+      <c r="M41">
         <v>191270</v>
       </c>
-      <c r="O41" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42">
         <v>67.858</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H42">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I42" s="1">
-        <v>1.704</v>
+        <v>115.63</v>
       </c>
       <c r="J42">
-        <v>115.630032</v>
+        <v>1.76</v>
       </c>
       <c r="K42" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L42" s="1">
-        <v>119.43008</v>
-      </c>
-      <c r="M42" t="s">
-        <v>115</v>
-      </c>
-      <c r="N42">
+        <v>119.43</v>
+      </c>
+      <c r="L42" t="s">
+        <v>114</v>
+      </c>
+      <c r="M42">
         <v>325266</v>
       </c>
-      <c r="O42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46233</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F43">
         <v>44.148</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H43">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I43" s="1">
-        <v>1.704</v>
+        <v>75.22799999999999</v>
       </c>
       <c r="J43">
-        <v>75.22819200000001</v>
+        <v>1.76</v>
       </c>
       <c r="K43" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L43" s="1">
-        <v>77.70048</v>
-      </c>
-      <c r="M43" t="s">
-        <v>116</v>
-      </c>
-      <c r="N43">
+        <v>77.7</v>
+      </c>
+      <c r="L43" t="s">
+        <v>115</v>
+      </c>
+      <c r="M43">
         <v>0</v>
       </c>
-      <c r="O43" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46233</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F44">
         <v>67.438</v>
       </c>
       <c r="G44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H44">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I44" s="1">
-        <v>1.704</v>
+        <v>114.914</v>
       </c>
       <c r="J44">
-        <v>114.914352</v>
+        <v>1.76</v>
       </c>
       <c r="K44" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L44" s="1">
-        <v>118.69088</v>
-      </c>
-      <c r="M44" t="s">
-        <v>117</v>
-      </c>
-      <c r="N44">
+        <v>118.691</v>
+      </c>
+      <c r="L44" t="s">
+        <v>116</v>
+      </c>
+      <c r="M44">
         <v>209696</v>
       </c>
-      <c r="O44" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>46233</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45">
         <v>75.97199999999999</v>
       </c>
       <c r="G45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H45">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I45" s="1">
-        <v>1.704</v>
+        <v>129.456</v>
       </c>
       <c r="J45">
-        <v>129.456288</v>
+        <v>1.79</v>
       </c>
       <c r="K45" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L45" s="1">
-        <v>135.98988</v>
-      </c>
-      <c r="M45" t="s">
-        <v>118</v>
-      </c>
-      <c r="N45">
+        <v>135.99</v>
+      </c>
+      <c r="L45" t="s">
+        <v>117</v>
+      </c>
+      <c r="M45">
         <v>226536</v>
       </c>
-      <c r="O45" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>46233</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F46">
         <v>31.361</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H46">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I46" s="1">
-        <v>1.489</v>
+        <v>46.697</v>
       </c>
       <c r="J46">
-        <v>46.696529</v>
+        <v>1.55</v>
       </c>
       <c r="K46" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L46" s="1">
-        <v>48.60955</v>
-      </c>
-      <c r="M46" t="s">
-        <v>119</v>
-      </c>
-      <c r="N46">
+        <v>48.61</v>
+      </c>
+      <c r="L46" t="s">
+        <v>118</v>
+      </c>
+      <c r="M46">
         <v>132219</v>
       </c>
-      <c r="O46" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F47">
         <v>22.587</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H47">
-        <v>1.459</v>
+        <v>1.499</v>
       </c>
       <c r="I47" s="1">
-        <v>1.499</v>
+        <v>33.858</v>
       </c>
       <c r="J47">
-        <v>33.857913</v>
+        <v>1.55</v>
       </c>
       <c r="K47" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L47" s="1">
-        <v>35.00985</v>
-      </c>
-      <c r="M47" t="s">
-        <v>120</v>
-      </c>
-      <c r="N47">
+        <v>35.01</v>
+      </c>
+      <c r="L47" t="s">
+        <v>119</v>
+      </c>
+      <c r="M47">
         <v>229742</v>
       </c>
-      <c r="O47" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48">
         <v>16.422</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H48">
         <v>0.64</v>
       </c>
       <c r="I48" s="1">
+        <v>10.51</v>
+      </c>
+      <c r="J48">
         <v>0.64</v>
       </c>
-      <c r="J48">
-        <v>10.51008</v>
-      </c>
       <c r="K48" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L48" s="1">
-        <v>10.51008</v>
-      </c>
-      <c r="M48" t="s">
-        <v>120</v>
-      </c>
-      <c r="N48">
+        <v>10.51</v>
+      </c>
+      <c r="L48" t="s">
+        <v>119</v>
+      </c>
+      <c r="M48">
         <v>229742</v>
       </c>
-      <c r="O48" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="3">
         <v>46234</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F49">
         <v>23.588</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H49">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I49" s="1">
-        <v>1.719</v>
+        <v>40.548</v>
       </c>
       <c r="J49">
-        <v>40.547772</v>
+        <v>1.77</v>
       </c>
       <c r="K49" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L49" s="1">
-        <v>41.75076</v>
-      </c>
-      <c r="M49" t="s">
-        <v>121</v>
-      </c>
-      <c r="N49">
+        <v>41.751</v>
+      </c>
+      <c r="L49" t="s">
+        <v>120</v>
+      </c>
+      <c r="M49">
         <v>209896</v>
       </c>
-      <c r="O49" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="3">
         <v>46234</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F50">
         <v>76.932</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H50">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I50" s="1">
-        <v>1.719</v>
+        <v>132.246</v>
       </c>
       <c r="J50">
-        <v>132.246108</v>
+        <v>1.77</v>
       </c>
       <c r="K50" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L50" s="1">
-        <v>136.16964</v>
-      </c>
-      <c r="M50" t="s">
-        <v>122</v>
-      </c>
-      <c r="N50">
+        <v>136.17</v>
+      </c>
+      <c r="L50" t="s">
+        <v>121</v>
+      </c>
+      <c r="M50">
         <v>252260</v>
       </c>
-      <c r="O50" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="3">
         <v>46234</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51">
         <v>55.748</v>
       </c>
       <c r="G51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H51">
-        <v>1.459</v>
+        <v>1.499</v>
       </c>
       <c r="I51" s="1">
-        <v>1.499</v>
+        <v>83.566</v>
       </c>
       <c r="J51">
-        <v>83.56625200000001</v>
+        <v>1.55</v>
       </c>
       <c r="K51" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L51" s="1">
-        <v>86.40940000000001</v>
-      </c>
-      <c r="M51" t="s">
-        <v>123</v>
-      </c>
-      <c r="N51">
+        <v>86.40900000000001</v>
+      </c>
+      <c r="L51" t="s">
+        <v>122</v>
+      </c>
+      <c r="M51">
         <v>0</v>
       </c>
-      <c r="O51" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="3">
         <v>46234</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F52">
         <v>12.632</v>
       </c>
       <c r="G52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H52">
-        <v>1.459</v>
+        <v>1.499</v>
       </c>
       <c r="I52" s="1">
-        <v>1.499</v>
+        <v>18.935</v>
       </c>
       <c r="J52">
-        <v>18.935368</v>
+        <v>1.55</v>
       </c>
       <c r="K52" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L52" s="1">
-        <v>19.5796</v>
-      </c>
-      <c r="M52" t="s">
-        <v>124</v>
-      </c>
-      <c r="N52">
+        <v>19.58</v>
+      </c>
+      <c r="L52" t="s">
+        <v>123</v>
+      </c>
+      <c r="M52">
         <v>132367</v>
       </c>
-      <c r="O52" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="3">
         <v>46234</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F53">
         <v>46.881</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H53">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I53" s="1">
-        <v>1.719</v>
+        <v>80.58799999999999</v>
       </c>
       <c r="J53">
-        <v>80.58843899999999</v>
+        <v>1.77</v>
       </c>
       <c r="K53" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L53" s="1">
-        <v>82.97937</v>
-      </c>
-      <c r="M53" t="s">
-        <v>121</v>
-      </c>
-      <c r="N53">
+        <v>82.979</v>
+      </c>
+      <c r="L53" t="s">
+        <v>120</v>
+      </c>
+      <c r="M53">
         <v>325631</v>
       </c>
-      <c r="O53" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="3">
         <v>46234</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F54">
         <v>38.331</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H54">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I54" s="1">
-        <v>1.719</v>
+        <v>65.89100000000001</v>
       </c>
       <c r="J54">
-        <v>65.890989</v>
+        <v>1.78</v>
       </c>
       <c r="K54" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L54" s="1">
-        <v>68.22918</v>
-      </c>
-      <c r="M54" t="s">
-        <v>125</v>
-      </c>
-      <c r="N54">
+        <v>68.229</v>
+      </c>
+      <c r="L54" t="s">
+        <v>124</v>
+      </c>
+      <c r="M54">
         <v>226919</v>
       </c>
-      <c r="O54" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="N54" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="3">
         <v>46234</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F55">
         <v>54.322</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H55">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I55" s="1">
-        <v>1.719</v>
+        <v>93.38</v>
       </c>
       <c r="J55">
-        <v>93.379518</v>
+        <v>1.77</v>
       </c>
       <c r="K55" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L55" s="1">
-        <v>96.14994</v>
-      </c>
-      <c r="M55" t="s">
-        <v>126</v>
-      </c>
-      <c r="N55">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="L55" t="s">
+        <v>125</v>
+      </c>
+      <c r="M55">
         <v>244564</v>
       </c>
-      <c r="O55" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="N55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="3">
         <v>46234</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F56">
         <v>0.61</v>
       </c>
       <c r="G56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H56">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I56" s="1">
-        <v>1.719</v>
+        <v>1.049</v>
       </c>
       <c r="J56">
-        <v>1.04859</v>
+        <v>1.77</v>
       </c>
       <c r="K56" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L56" s="1">
-        <v>1.0797</v>
-      </c>
-      <c r="M56" t="s">
-        <v>127</v>
-      </c>
-      <c r="N56">
+        <v>1.08</v>
+      </c>
+      <c r="L56" t="s">
+        <v>126</v>
+      </c>
+      <c r="M56">
         <v>0</v>
       </c>
-      <c r="O56" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="N56" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="3">
         <v>46234</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F57">
         <v>73.503</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H57">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I57" s="1">
-        <v>1.719</v>
+        <v>126.352</v>
       </c>
       <c r="J57">
-        <v>126.351657</v>
+        <v>1.77</v>
       </c>
       <c r="K57" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L57" s="1">
-        <v>130.10031</v>
-      </c>
-      <c r="M57" t="s">
-        <v>128</v>
-      </c>
-      <c r="N57">
+        <v>130.1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>127</v>
+      </c>
+      <c r="M57">
         <v>27664</v>
       </c>
-      <c r="O57" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="N57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="3">
         <v>46234</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F58">
         <v>27.59</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H58">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I58" s="1">
-        <v>1.719</v>
+        <v>47.427</v>
       </c>
       <c r="J58">
-        <v>47.42721</v>
+        <v>1.78</v>
       </c>
       <c r="K58" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L58" s="1">
-        <v>49.1102</v>
-      </c>
-      <c r="M58" t="s">
-        <v>129</v>
-      </c>
-      <c r="N58">
+        <v>49.11</v>
+      </c>
+      <c r="L58" t="s">
+        <v>128</v>
+      </c>
+      <c r="M58">
         <v>0</v>
       </c>
-      <c r="O58" t="s">
+      <c r="N58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="4" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
-      <c r="A61" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3746,109 +3569,109 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:14">
       <c r="A62" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="E62" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="7">
         <v>4469.9</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="8">
         <v>46</v>
       </c>
       <c r="D63" s="8">
-        <v>1.629611</v>
-      </c>
-      <c r="E63" s="7">
-        <v>7284.2</v>
-      </c>
-      <c r="F63" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="E63" s="8">
+        <v>7284.199</v>
+      </c>
+      <c r="F63" s="8">
         <v>7604.81</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:14">
       <c r="A64" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="7">
         <v>319.893</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="8">
         <v>9</v>
       </c>
       <c r="D64" s="8">
-        <v>1.468745</v>
-      </c>
-      <c r="E64" s="7">
-        <v>469.84</v>
-      </c>
-      <c r="F64" s="7">
-        <v>494.09</v>
+        <v>1.469</v>
+      </c>
+      <c r="E64" s="8">
+        <v>469.841</v>
+      </c>
+      <c r="F64" s="8">
+        <v>494.086</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="7">
         <v>61.99</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="8">
         <v>1</v>
       </c>
       <c r="D65" s="8">
         <v>1.91</v>
       </c>
-      <c r="E65" s="7">
-        <v>118.4</v>
-      </c>
-      <c r="F65" s="7">
-        <v>118.4</v>
+      <c r="E65" s="8">
+        <v>118.401</v>
+      </c>
+      <c r="F65" s="8">
+        <v>118.401</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="7">
         <v>16.422</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <v>1</v>
       </c>
       <c r="D66" s="8">
         <v>0.64</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="8">
         <v>10.51</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="8">
         <v>10.51</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B67" s="10">
         <v>4868.205</v>
@@ -3858,10 +3681,10 @@
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="10">
-        <v>7882.95</v>
+        <v>7882.951</v>
       </c>
       <c r="F67" s="10">
-        <v>8227.809999999999</v>
+        <v>8227.807000000001</v>
       </c>
     </row>
   </sheetData>
